--- a/outputs/daily/hr_rankings_2026-10-23.xlsx
+++ b/outputs/daily/hr_rankings_2026-10-23.xlsx
@@ -760,12 +760,12 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -784,7 +784,7 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>53</v>
+        <v>56.1</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P2" t="n">
@@ -808,10 +808,10 @@
         <v>34.3</v>
       </c>
       <c r="R2" t="n">
-        <v>27.6</v>
+        <v>41.1</v>
       </c>
       <c r="S2" t="n">
-        <v>92.09999999999999</v>
+        <v>100</v>
       </c>
       <c r="T2" t="n">
         <v>80</v>
@@ -821,14 +821,14 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="X2" t="inlineStr">
         <is>
           <t>3</t>
@@ -846,12 +846,12 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
+          <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>lineup projected / unconfirmed</t>
+          <t>RotoWire not confirmed; order MLB 2 vs RotoWire 3</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -996,8 +996,16 @@
           <t>28.96</t>
         </is>
       </c>
-      <c r="BG2" t="inlineStr"/>
-      <c r="BH2" t="inlineStr"/>
+      <c r="BG2" t="inlineStr">
+        <is>
+          <t>L To R</t>
+        </is>
+      </c>
+      <c r="BH2" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
       <c r="BI2" t="inlineStr">
         <is>
           <t>American Family Field</t>
@@ -1036,7 +1044,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -1060,7 +1068,7 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>49</v>
+        <v>51.6</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -1074,7 +1082,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
+          <t>Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P3" t="n">
@@ -1084,10 +1092,10 @@
         <v>34.3</v>
       </c>
       <c r="R3" t="n">
-        <v>27.6</v>
+        <v>41.1</v>
       </c>
       <c r="S3" t="n">
-        <v>88.7</v>
+        <v>93.2</v>
       </c>
       <c r="T3" t="n">
         <v>50</v>
@@ -1097,14 +1105,14 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="X3" t="inlineStr">
         <is>
           <t>1</t>
@@ -1122,12 +1130,12 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
+          <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>lineup projected / unconfirmed</t>
+          <t>RotoWire not confirmed</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -1272,8 +1280,16 @@
           <t>28.96</t>
         </is>
       </c>
-      <c r="BG3" t="inlineStr"/>
-      <c r="BH3" t="inlineStr"/>
+      <c r="BG3" t="inlineStr">
+        <is>
+          <t>L To R</t>
+        </is>
+      </c>
+      <c r="BH3" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
       <c r="BI3" t="inlineStr">
         <is>
           <t>American Family Field</t>
@@ -1312,7 +1328,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -1336,7 +1352,7 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>48.3</v>
+        <v>50.4</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -1360,7 +1376,7 @@
         <v>18.6</v>
       </c>
       <c r="R4" t="n">
-        <v>27.6</v>
+        <v>41.1</v>
       </c>
       <c r="S4" t="n">
         <v>92.09999999999999</v>
@@ -1548,8 +1564,16 @@
           <t>25.57</t>
         </is>
       </c>
-      <c r="BG4" t="inlineStr"/>
-      <c r="BH4" t="inlineStr"/>
+      <c r="BG4" t="inlineStr">
+        <is>
+          <t>L To R</t>
+        </is>
+      </c>
+      <c r="BH4" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
       <c r="BI4" t="inlineStr">
         <is>
           <t>American Family Field</t>
@@ -1563,12 +1587,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>668930</t>
+          <t>592885</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Brice Turang</t>
+          <t>Christian Yelich</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1588,12 +1612,12 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1612,7 +1636,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>48.3</v>
+        <v>49</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -1626,40 +1650,40 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P5" t="n">
-        <v>36.6</v>
+        <v>38.2</v>
       </c>
       <c r="Q5" t="n">
         <v>34.3</v>
       </c>
       <c r="R5" t="n">
-        <v>27.6</v>
+        <v>41.1</v>
       </c>
       <c r="S5" t="n">
-        <v>95.5</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T5" t="n">
         <v>80</v>
       </c>
       <c r="U5" t="n">
-        <v>65.2</v>
+        <v>25.3</v>
       </c>
       <c r="V5" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -1674,12 +1698,12 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
+          <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>lineup projected / unconfirmed</t>
+          <t>RotoWire not confirmed; order MLB 3 vs RotoWire 6</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1701,22 +1725,22 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 4/24, 1 HR</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
@@ -1731,67 +1755,67 @@
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>7.79</t>
+          <t>9.81</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>43.34</t>
+          <t>43.95</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>90.54</t>
+          <t>89.29</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>100.4264</t>
+          <t>100.9775</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>0.4283</t>
+          <t>0.4012</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>0.1712</t>
+          <t>0.1674</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>0.3413</t>
+          <t>0.3146</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>70.25</t>
+          <t>73.23</t>
         </is>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>13.2</t>
+          <t>32.32</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>28.21</t>
+          <t>34.24</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>23.43</t>
+          <t>19.09</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>20.1</t>
+          <t>17.1</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>0.1715</t>
+          <t>0.1565</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
@@ -1824,8 +1848,16 @@
           <t>28.96</t>
         </is>
       </c>
-      <c r="BG5" t="inlineStr"/>
-      <c r="BH5" t="inlineStr"/>
+      <c r="BG5" t="inlineStr">
+        <is>
+          <t>L To R</t>
+        </is>
+      </c>
+      <c r="BH5" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
       <c r="BI5" t="inlineStr">
         <is>
           <t>American Family Field</t>
@@ -1839,12 +1871,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>669003</t>
+          <t>668930</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Garrett Mitchell</t>
+          <t>Brice Turang</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1864,7 +1896,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1888,7 +1920,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>47.2</v>
+        <v>49</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -1902,40 +1934,40 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P6" t="n">
-        <v>47.1</v>
+        <v>36.6</v>
       </c>
       <c r="Q6" t="n">
         <v>34.3</v>
       </c>
       <c r="R6" t="n">
-        <v>27.6</v>
+        <v>41.1</v>
       </c>
       <c r="S6" t="n">
-        <v>81.90000000000001</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T6" t="n">
         <v>80</v>
       </c>
       <c r="U6" t="n">
-        <v>13.3</v>
+        <v>65.2</v>
       </c>
       <c r="V6" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
@@ -1950,12 +1982,12 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
+          <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>lineup projected / unconfirmed</t>
+          <t>RotoWire not confirmed; order MLB 5 vs RotoWire 2</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1977,22 +2009,22 @@
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/24, 0 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
@@ -2002,72 +2034,72 @@
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>EV profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>10.2</t>
+          <t>7.79</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>49.55</t>
+          <t>43.34</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>92.36</t>
+          <t>90.54</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>103.8477</t>
+          <t>100.4264</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>0.4152</t>
+          <t>0.4283</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>0.1589</t>
+          <t>0.1712</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>0.3335</t>
+          <t>0.3413</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>77.15</t>
+          <t>70.25</t>
         </is>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>77.37</t>
+          <t>13.2</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>32.81</t>
+          <t>28.21</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>16.78</t>
+          <t>23.43</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>20.1</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>0.1342</t>
+          <t>0.1715</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
@@ -2100,8 +2132,16 @@
           <t>28.96</t>
         </is>
       </c>
-      <c r="BG6" t="inlineStr"/>
-      <c r="BH6" t="inlineStr"/>
+      <c r="BG6" t="inlineStr">
+        <is>
+          <t>L To R</t>
+        </is>
+      </c>
+      <c r="BH6" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
       <c r="BI6" t="inlineStr">
         <is>
           <t>American Family Field</t>
@@ -2140,7 +2180,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -2164,7 +2204,7 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>46.7</v>
+        <v>48.8</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -2188,7 +2228,7 @@
         <v>18.6</v>
       </c>
       <c r="R7" t="n">
-        <v>27.6</v>
+        <v>41.1</v>
       </c>
       <c r="S7" t="n">
         <v>95.5</v>
@@ -2376,8 +2416,16 @@
           <t>25.57</t>
         </is>
       </c>
-      <c r="BG7" t="inlineStr"/>
-      <c r="BH7" t="inlineStr"/>
+      <c r="BG7" t="inlineStr">
+        <is>
+          <t>L To R</t>
+        </is>
+      </c>
+      <c r="BH7" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
       <c r="BI7" t="inlineStr">
         <is>
           <t>American Family Field</t>
@@ -2391,12 +2439,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>661388</t>
+          <t>669003</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>William Contreras</t>
+          <t>Garrett Mitchell</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -2416,12 +2464,12 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -2440,7 +2488,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>44.5</v>
+        <v>48.5</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -2454,40 +2502,40 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Strong Barrel, Platoon Edge</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>39.5</v>
+        <v>47.1</v>
       </c>
       <c r="Q8" t="n">
         <v>34.3</v>
       </c>
       <c r="R8" t="n">
-        <v>27.6</v>
+        <v>41.1</v>
       </c>
       <c r="S8" t="n">
-        <v>90.40000000000001</v>
+        <v>76.2</v>
       </c>
       <c r="T8" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U8" t="n">
-        <v>37.8</v>
+        <v>13.3</v>
       </c>
       <c r="V8" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
@@ -2502,12 +2550,12 @@
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
+          <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>lineup projected / unconfirmed</t>
+          <t>RotoWire not confirmed; order MLB 6 vs RotoWire 5</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -2529,7 +2577,7 @@
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
@@ -2539,87 +2587,87 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/24, 1 HR</t>
+          <t>Last 7 games: 5/24, 0 HR</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 6.9% barrel, 22.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.9% barrel, 22.0 HR allowed</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>EV profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>7.87</t>
+          <t>10.2</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>45.42</t>
+          <t>49.55</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>90.54</t>
+          <t>92.36</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>101.6393</t>
+          <t>103.8477</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>0.4266</t>
+          <t>0.4152</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>0.1702</t>
+          <t>0.1589</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>0.3322</t>
+          <t>0.3335</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
         <is>
-          <t>73.41</t>
+          <t>77.15</t>
         </is>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>36.44</t>
+          <t>77.37</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>36.04</t>
+          <t>32.81</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>24.43</t>
+          <t>16.78</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>17.7</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>0.1446</t>
+          <t>0.1342</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
@@ -2652,8 +2700,16 @@
           <t>28.96</t>
         </is>
       </c>
-      <c r="BG8" t="inlineStr"/>
-      <c r="BH8" t="inlineStr"/>
+      <c r="BG8" t="inlineStr">
+        <is>
+          <t>L To R</t>
+        </is>
+      </c>
+      <c r="BH8" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
       <c r="BI8" t="inlineStr">
         <is>
           <t>American Family Field</t>
@@ -2667,12 +2723,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>592885</t>
+          <t>661388</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Christian Yelich</t>
+          <t>William Contreras</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2692,12 +2748,12 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -2716,7 +2772,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>43.5</v>
+        <v>47.1</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -2730,40 +2786,40 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P9" t="n">
-        <v>38.2</v>
+        <v>39.5</v>
       </c>
       <c r="Q9" t="n">
         <v>34.3</v>
       </c>
       <c r="R9" t="n">
-        <v>27.6</v>
+        <v>41.1</v>
       </c>
       <c r="S9" t="n">
-        <v>71.7</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T9" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U9" t="n">
-        <v>25.3</v>
+        <v>37.8</v>
       </c>
       <c r="V9" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
@@ -2778,12 +2834,12 @@
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
+          <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>lineup projected / unconfirmed</t>
+          <t>RotoWire not confirmed</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -2805,7 +2861,7 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
@@ -2820,12 +2876,12 @@
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/24, 1 HR</t>
+          <t>Last 7 games: 6/24, 1 HR</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.9% barrel, 22.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 6.9% barrel, 22.0 HR allowed</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
@@ -2835,67 +2891,67 @@
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>9.81</t>
+          <t>7.87</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>43.95</t>
+          <t>45.42</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>89.29</t>
+          <t>90.54</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>100.9775</t>
+          <t>101.6393</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>0.4012</t>
+          <t>0.4266</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>0.1674</t>
+          <t>0.1702</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>0.3146</t>
+          <t>0.3322</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
         <is>
-          <t>73.23</t>
+          <t>73.41</t>
         </is>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>32.32</t>
+          <t>36.44</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>34.24</t>
+          <t>36.04</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>19.09</t>
+          <t>24.43</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>17.1</t>
+          <t>17.7</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>0.1565</t>
+          <t>0.1446</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
@@ -2928,8 +2984,16 @@
           <t>28.96</t>
         </is>
       </c>
-      <c r="BG9" t="inlineStr"/>
-      <c r="BH9" t="inlineStr"/>
+      <c r="BG9" t="inlineStr">
+        <is>
+          <t>L To R</t>
+        </is>
+      </c>
+      <c r="BH9" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
       <c r="BI9" t="inlineStr">
         <is>
           <t>American Family Field</t>
@@ -2968,7 +3032,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -2992,7 +3056,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -3016,7 +3080,7 @@
         <v>18.6</v>
       </c>
       <c r="R10" t="n">
-        <v>27.6</v>
+        <v>41.1</v>
       </c>
       <c r="S10" t="n">
         <v>71.7</v>
@@ -3204,8 +3268,16 @@
           <t>25.57</t>
         </is>
       </c>
-      <c r="BG10" t="inlineStr"/>
-      <c r="BH10" t="inlineStr"/>
+      <c r="BG10" t="inlineStr">
+        <is>
+          <t>L To R</t>
+        </is>
+      </c>
+      <c r="BH10" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
       <c r="BI10" t="inlineStr">
         <is>
           <t>American Family Field</t>
@@ -3244,7 +3316,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -3268,7 +3340,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>40.1</v>
+        <v>42.1</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -3292,7 +3364,7 @@
         <v>18.6</v>
       </c>
       <c r="R11" t="n">
-        <v>27.6</v>
+        <v>41.1</v>
       </c>
       <c r="S11" t="n">
         <v>88.7</v>
@@ -3480,8 +3552,16 @@
           <t>25.57</t>
         </is>
       </c>
-      <c r="BG11" t="inlineStr"/>
-      <c r="BH11" t="inlineStr"/>
+      <c r="BG11" t="inlineStr">
+        <is>
+          <t>L To R</t>
+        </is>
+      </c>
+      <c r="BH11" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
       <c r="BI11" t="inlineStr">
         <is>
           <t>American Family Field</t>
@@ -3520,7 +3600,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -3544,7 +3624,7 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -3568,7 +3648,7 @@
         <v>18.6</v>
       </c>
       <c r="R12" t="n">
-        <v>27.6</v>
+        <v>41.1</v>
       </c>
       <c r="S12" t="n">
         <v>90.40000000000001</v>
@@ -3756,8 +3836,16 @@
           <t>25.57</t>
         </is>
       </c>
-      <c r="BG12" t="inlineStr"/>
-      <c r="BH12" t="inlineStr"/>
+      <c r="BG12" t="inlineStr">
+        <is>
+          <t>L To R</t>
+        </is>
+      </c>
+      <c r="BH12" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
       <c r="BI12" t="inlineStr">
         <is>
           <t>American Family Field</t>
@@ -3771,12 +3859,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>800325</t>
+          <t>666152</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Luis Lara</t>
+          <t>David Hamilton</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -3796,12 +3884,12 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -3820,7 +3908,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>31.1</v>
+        <v>32.7</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -3834,65 +3922,57 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P13" t="n">
-        <v>16.6</v>
+        <v>11.1</v>
       </c>
       <c r="Q13" t="n">
-        <v>32.5</v>
+        <v>34.3</v>
       </c>
       <c r="R13" t="n">
-        <v>27.6</v>
+        <v>41.1</v>
       </c>
       <c r="S13" t="n">
-        <v>47.9</v>
+        <v>44.8</v>
       </c>
       <c r="T13" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="U13" t="n">
-        <v>5.1</v>
+        <v>23.7</v>
       </c>
       <c r="V13" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr"/>
+      <c r="X13" t="inlineStr"/>
+      <c r="Y13" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X13" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Y13" t="inlineStr">
+      <c r="Z13" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
+          <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>lineup projected / unconfirmed</t>
+          <t>not found on RotoWire</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD13" t="inlineStr"/>
@@ -3909,12 +3989,12 @@
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
@@ -3924,12 +4004,12 @@
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/26, 0 HR</t>
+          <t>Last 7 games: 5/18, 0 HR</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 6.9% barrel, 22.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.9% barrel, 22.0 HR allowed</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
@@ -3939,67 +4019,67 @@
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>3.4</t>
+          <t>4.18</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>41.5</t>
+          <t>27.87</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>86.74</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>98.8409</t>
+          <t>96.8019</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>0.331</t>
+          <t>0.3169</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
         <is>
-          <t>0.075</t>
+          <t>0.0967</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>0.293</t>
+          <t>0.2712</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
         <is>
-          <t>71.4</t>
+          <t>69.66</t>
         </is>
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>16.7</t>
+          <t>6.59</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>30.6</t>
+          <t>35.88</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>15.0</t>
+          <t>24.48</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>4.6</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>0.079</t>
+          <t>0.1042</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
@@ -4032,8 +4112,16 @@
           <t>28.96</t>
         </is>
       </c>
-      <c r="BG13" t="inlineStr"/>
-      <c r="BH13" t="inlineStr"/>
+      <c r="BG13" t="inlineStr">
+        <is>
+          <t>L To R</t>
+        </is>
+      </c>
+      <c r="BH13" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
       <c r="BI13" t="inlineStr">
         <is>
           <t>American Family Field</t>
@@ -4072,7 +4160,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -4096,7 +4184,7 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>30</v>
+        <v>32.6</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -4110,7 +4198,7 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>No major boost</t>
         </is>
       </c>
       <c r="P14" t="n">
@@ -4120,10 +4208,10 @@
         <v>34.3</v>
       </c>
       <c r="R14" t="n">
-        <v>27.6</v>
+        <v>41.1</v>
       </c>
       <c r="S14" t="n">
-        <v>59.8</v>
+        <v>64.3</v>
       </c>
       <c r="T14" t="n">
         <v>50</v>
@@ -4133,14 +4221,14 @@
       </c>
       <c r="V14" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="X14" t="inlineStr">
         <is>
           <t>7</t>
@@ -4158,12 +4246,12 @@
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
+          <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>lineup projected / unconfirmed</t>
+          <t>RotoWire not confirmed</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
@@ -4308,8 +4396,16 @@
           <t>28.96</t>
         </is>
       </c>
-      <c r="BG14" t="inlineStr"/>
-      <c r="BH14" t="inlineStr"/>
+      <c r="BG14" t="inlineStr">
+        <is>
+          <t>L To R</t>
+        </is>
+      </c>
+      <c r="BH14" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
       <c r="BI14" t="inlineStr">
         <is>
           <t>American Family Field</t>
@@ -4323,12 +4419,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>687401</t>
+          <t>686217</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Joey Ortiz</t>
+          <t>Sal Frelick</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -4348,12 +4444,12 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -4372,7 +4468,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>29.3</v>
+        <v>31.6</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -4386,60 +4482,52 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P15" t="n">
-        <v>17.1</v>
+        <v>5.4</v>
       </c>
       <c r="Q15" t="n">
         <v>34.3</v>
       </c>
       <c r="R15" t="n">
-        <v>27.6</v>
+        <v>41.1</v>
       </c>
       <c r="S15" t="n">
-        <v>40.2</v>
+        <v>52.4</v>
       </c>
       <c r="T15" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U15" t="n">
-        <v>22.4</v>
+        <v>17.3</v>
       </c>
       <c r="V15" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr"/>
+      <c r="X15" t="inlineStr"/>
+      <c r="Y15" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X15" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="Y15" t="inlineStr">
+      <c r="Z15" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
+          <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>lineup projected / unconfirmed</t>
+          <t>not found on RotoWire</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
@@ -4461,12 +4549,12 @@
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>17</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
@@ -4476,12 +4564,12 @@
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>Last 7 games: 7/26, 0 HR</t>
+          <t>Last 7 games: 4/17, 0 HR</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 6.9% barrel, 22.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.9% barrel, 22.0 HR allowed</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
@@ -4491,67 +4579,67 @@
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>3.7</t>
+          <t>2.54</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>36.16</t>
+          <t>26.98</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>87.91</t>
+          <t>85.64</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>99.2209</t>
+          <t>96.2217</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>0.3403</t>
+          <t>0.3285</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
         <is>
-          <t>0.0967</t>
+          <t>0.0826</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>0.2904</t>
+          <t>0.2864</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>68.24</t>
         </is>
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>30.57</t>
+          <t>3.76</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>31.91</t>
+          <t>39.46</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>19.68</t>
+          <t>20.9</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>6.4</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>0.1185</t>
+          <t>0.0974</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
@@ -4584,8 +4672,16 @@
           <t>28.96</t>
         </is>
       </c>
-      <c r="BG15" t="inlineStr"/>
-      <c r="BH15" t="inlineStr"/>
+      <c r="BG15" t="inlineStr">
+        <is>
+          <t>L To R</t>
+        </is>
+      </c>
+      <c r="BH15" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
       <c r="BI15" t="inlineStr">
         <is>
           <t>American Family Field</t>
@@ -4624,7 +4720,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -4648,7 +4744,7 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>28.6</v>
+        <v>30.6</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -4672,7 +4768,7 @@
         <v>18.6</v>
       </c>
       <c r="R16" t="n">
-        <v>27.6</v>
+        <v>41.1</v>
       </c>
       <c r="S16" t="n">
         <v>47.9</v>
@@ -4860,8 +4956,16 @@
           <t>25.57</t>
         </is>
       </c>
-      <c r="BG16" t="inlineStr"/>
-      <c r="BH16" t="inlineStr"/>
+      <c r="BG16" t="inlineStr">
+        <is>
+          <t>L To R</t>
+        </is>
+      </c>
+      <c r="BH16" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
       <c r="BI16" t="inlineStr">
         <is>
           <t>American Family Field</t>
@@ -4900,7 +5004,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -4924,7 +5028,7 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>28.5</v>
+        <v>30.5</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -4948,7 +5052,7 @@
         <v>18.6</v>
       </c>
       <c r="R17" t="n">
-        <v>27.6</v>
+        <v>41.1</v>
       </c>
       <c r="S17" t="n">
         <v>59.8</v>
@@ -5136,8 +5240,16 @@
           <t>25.57</t>
         </is>
       </c>
-      <c r="BG17" t="inlineStr"/>
-      <c r="BH17" t="inlineStr"/>
+      <c r="BG17" t="inlineStr">
+        <is>
+          <t>L To R</t>
+        </is>
+      </c>
+      <c r="BH17" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
       <c r="BI17" t="inlineStr">
         <is>
           <t>American Family Field</t>
@@ -5176,7 +5288,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -5200,7 +5312,7 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>28.1</v>
+        <v>30.1</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -5224,7 +5336,7 @@
         <v>18.6</v>
       </c>
       <c r="R18" t="n">
-        <v>27.6</v>
+        <v>41.1</v>
       </c>
       <c r="S18" t="n">
         <v>81.90000000000001</v>
@@ -5412,8 +5524,16 @@
           <t>25.57</t>
         </is>
       </c>
-      <c r="BG18" t="inlineStr"/>
-      <c r="BH18" t="inlineStr"/>
+      <c r="BG18" t="inlineStr">
+        <is>
+          <t>L To R</t>
+        </is>
+      </c>
+      <c r="BH18" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
       <c r="BI18" t="inlineStr">
         <is>
           <t>American Family Field</t>
@@ -5452,7 +5572,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -5476,7 +5596,7 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>23.9</v>
+        <v>25.9</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -5500,7 +5620,7 @@
         <v>17.3</v>
       </c>
       <c r="R19" t="n">
-        <v>27.6</v>
+        <v>41.1</v>
       </c>
       <c r="S19" t="n">
         <v>40.2</v>
@@ -5688,8 +5808,16 @@
           <t>25.57</t>
         </is>
       </c>
-      <c r="BG19" t="inlineStr"/>
-      <c r="BH19" t="inlineStr"/>
+      <c r="BG19" t="inlineStr">
+        <is>
+          <t>L To R</t>
+        </is>
+      </c>
+      <c r="BH19" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
       <c r="BI19" t="inlineStr">
         <is>
           <t>American Family Field</t>
@@ -6054,12 +6182,12 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -6078,7 +6206,7 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>53</v>
+        <v>56.1</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -6092,7 +6220,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P2" t="n">
@@ -6102,10 +6230,10 @@
         <v>34.3</v>
       </c>
       <c r="R2" t="n">
-        <v>27.6</v>
+        <v>41.1</v>
       </c>
       <c r="S2" t="n">
-        <v>92.09999999999999</v>
+        <v>100</v>
       </c>
       <c r="T2" t="n">
         <v>80</v>
@@ -6115,14 +6243,14 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="X2" t="inlineStr">
         <is>
           <t>3</t>
@@ -6140,12 +6268,12 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
+          <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>lineup projected / unconfirmed</t>
+          <t>RotoWire not confirmed; order MLB 2 vs RotoWire 3</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -6290,8 +6418,16 @@
           <t>28.96</t>
         </is>
       </c>
-      <c r="BG2" t="inlineStr"/>
-      <c r="BH2" t="inlineStr"/>
+      <c r="BG2" t="inlineStr">
+        <is>
+          <t>L To R</t>
+        </is>
+      </c>
+      <c r="BH2" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
       <c r="BI2" t="inlineStr">
         <is>
           <t>American Family Field</t>
@@ -6330,7 +6466,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -6354,7 +6490,7 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>49</v>
+        <v>51.6</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -6368,7 +6504,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
+          <t>Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P3" t="n">
@@ -6378,10 +6514,10 @@
         <v>34.3</v>
       </c>
       <c r="R3" t="n">
-        <v>27.6</v>
+        <v>41.1</v>
       </c>
       <c r="S3" t="n">
-        <v>88.7</v>
+        <v>93.2</v>
       </c>
       <c r="T3" t="n">
         <v>50</v>
@@ -6391,14 +6527,14 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="X3" t="inlineStr">
         <is>
           <t>1</t>
@@ -6416,12 +6552,12 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
+          <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>lineup projected / unconfirmed</t>
+          <t>RotoWire not confirmed</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -6566,8 +6702,16 @@
           <t>28.96</t>
         </is>
       </c>
-      <c r="BG3" t="inlineStr"/>
-      <c r="BH3" t="inlineStr"/>
+      <c r="BG3" t="inlineStr">
+        <is>
+          <t>L To R</t>
+        </is>
+      </c>
+      <c r="BH3" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
       <c r="BI3" t="inlineStr">
         <is>
           <t>American Family Field</t>
@@ -6606,7 +6750,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -6630,7 +6774,7 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>48.3</v>
+        <v>50.4</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -6654,7 +6798,7 @@
         <v>18.6</v>
       </c>
       <c r="R4" t="n">
-        <v>27.6</v>
+        <v>41.1</v>
       </c>
       <c r="S4" t="n">
         <v>92.09999999999999</v>
@@ -6842,8 +6986,16 @@
           <t>25.57</t>
         </is>
       </c>
-      <c r="BG4" t="inlineStr"/>
-      <c r="BH4" t="inlineStr"/>
+      <c r="BG4" t="inlineStr">
+        <is>
+          <t>L To R</t>
+        </is>
+      </c>
+      <c r="BH4" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
       <c r="BI4" t="inlineStr">
         <is>
           <t>American Family Field</t>
@@ -6857,12 +7009,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>668930</t>
+          <t>592885</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Brice Turang</t>
+          <t>Christian Yelich</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -6882,12 +7034,12 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -6906,7 +7058,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>48.3</v>
+        <v>49</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -6920,40 +7072,40 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P5" t="n">
-        <v>36.6</v>
+        <v>38.2</v>
       </c>
       <c r="Q5" t="n">
         <v>34.3</v>
       </c>
       <c r="R5" t="n">
-        <v>27.6</v>
+        <v>41.1</v>
       </c>
       <c r="S5" t="n">
-        <v>95.5</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T5" t="n">
         <v>80</v>
       </c>
       <c r="U5" t="n">
-        <v>65.2</v>
+        <v>25.3</v>
       </c>
       <c r="V5" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -6968,12 +7120,12 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
+          <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>lineup projected / unconfirmed</t>
+          <t>RotoWire not confirmed; order MLB 3 vs RotoWire 6</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -6995,22 +7147,22 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 4/24, 1 HR</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
@@ -7025,67 +7177,67 @@
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>7.79</t>
+          <t>9.81</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>43.34</t>
+          <t>43.95</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>90.54</t>
+          <t>89.29</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>100.4264</t>
+          <t>100.9775</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>0.4283</t>
+          <t>0.4012</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>0.1712</t>
+          <t>0.1674</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>0.3413</t>
+          <t>0.3146</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>70.25</t>
+          <t>73.23</t>
         </is>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>13.2</t>
+          <t>32.32</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>28.21</t>
+          <t>34.24</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>23.43</t>
+          <t>19.09</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>20.1</t>
+          <t>17.1</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>0.1715</t>
+          <t>0.1565</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
@@ -7118,8 +7270,16 @@
           <t>28.96</t>
         </is>
       </c>
-      <c r="BG5" t="inlineStr"/>
-      <c r="BH5" t="inlineStr"/>
+      <c r="BG5" t="inlineStr">
+        <is>
+          <t>L To R</t>
+        </is>
+      </c>
+      <c r="BH5" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
       <c r="BI5" t="inlineStr">
         <is>
           <t>American Family Field</t>
@@ -7133,12 +7293,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>669003</t>
+          <t>668930</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Garrett Mitchell</t>
+          <t>Brice Turang</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -7158,7 +7318,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -7182,7 +7342,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>47.2</v>
+        <v>49</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -7196,40 +7356,40 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P6" t="n">
-        <v>47.1</v>
+        <v>36.6</v>
       </c>
       <c r="Q6" t="n">
         <v>34.3</v>
       </c>
       <c r="R6" t="n">
-        <v>27.6</v>
+        <v>41.1</v>
       </c>
       <c r="S6" t="n">
-        <v>81.90000000000001</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T6" t="n">
         <v>80</v>
       </c>
       <c r="U6" t="n">
-        <v>13.3</v>
+        <v>65.2</v>
       </c>
       <c r="V6" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
@@ -7244,12 +7404,12 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
+          <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>lineup projected / unconfirmed</t>
+          <t>RotoWire not confirmed; order MLB 5 vs RotoWire 2</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -7271,22 +7431,22 @@
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/24, 0 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
@@ -7296,72 +7456,72 @@
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>EV profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>10.2</t>
+          <t>7.79</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>49.55</t>
+          <t>43.34</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>92.36</t>
+          <t>90.54</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>103.8477</t>
+          <t>100.4264</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>0.4152</t>
+          <t>0.4283</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>0.1589</t>
+          <t>0.1712</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>0.3335</t>
+          <t>0.3413</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>77.15</t>
+          <t>70.25</t>
         </is>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>77.37</t>
+          <t>13.2</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>32.81</t>
+          <t>28.21</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>16.78</t>
+          <t>23.43</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>20.1</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>0.1342</t>
+          <t>0.1715</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
@@ -7394,8 +7554,16 @@
           <t>28.96</t>
         </is>
       </c>
-      <c r="BG6" t="inlineStr"/>
-      <c r="BH6" t="inlineStr"/>
+      <c r="BG6" t="inlineStr">
+        <is>
+          <t>L To R</t>
+        </is>
+      </c>
+      <c r="BH6" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
       <c r="BI6" t="inlineStr">
         <is>
           <t>American Family Field</t>
@@ -7434,7 +7602,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -7458,7 +7626,7 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>46.7</v>
+        <v>48.8</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -7482,7 +7650,7 @@
         <v>18.6</v>
       </c>
       <c r="R7" t="n">
-        <v>27.6</v>
+        <v>41.1</v>
       </c>
       <c r="S7" t="n">
         <v>95.5</v>
@@ -7670,8 +7838,16 @@
           <t>25.57</t>
         </is>
       </c>
-      <c r="BG7" t="inlineStr"/>
-      <c r="BH7" t="inlineStr"/>
+      <c r="BG7" t="inlineStr">
+        <is>
+          <t>L To R</t>
+        </is>
+      </c>
+      <c r="BH7" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
       <c r="BI7" t="inlineStr">
         <is>
           <t>American Family Field</t>
@@ -7685,12 +7861,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>661388</t>
+          <t>669003</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>William Contreras</t>
+          <t>Garrett Mitchell</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -7710,12 +7886,12 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -7734,7 +7910,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>44.5</v>
+        <v>48.5</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -7748,40 +7924,40 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Strong Barrel, Platoon Edge</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>39.5</v>
+        <v>47.1</v>
       </c>
       <c r="Q8" t="n">
         <v>34.3</v>
       </c>
       <c r="R8" t="n">
-        <v>27.6</v>
+        <v>41.1</v>
       </c>
       <c r="S8" t="n">
-        <v>90.40000000000001</v>
+        <v>76.2</v>
       </c>
       <c r="T8" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U8" t="n">
-        <v>37.8</v>
+        <v>13.3</v>
       </c>
       <c r="V8" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
@@ -7796,12 +7972,12 @@
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
+          <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>lineup projected / unconfirmed</t>
+          <t>RotoWire not confirmed; order MLB 6 vs RotoWire 5</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -7823,7 +7999,7 @@
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
@@ -7833,87 +8009,87 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/24, 1 HR</t>
+          <t>Last 7 games: 5/24, 0 HR</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 6.9% barrel, 22.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.9% barrel, 22.0 HR allowed</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>EV profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>7.87</t>
+          <t>10.2</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>45.42</t>
+          <t>49.55</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>90.54</t>
+          <t>92.36</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>101.6393</t>
+          <t>103.8477</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>0.4266</t>
+          <t>0.4152</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>0.1702</t>
+          <t>0.1589</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>0.3322</t>
+          <t>0.3335</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
         <is>
-          <t>73.41</t>
+          <t>77.15</t>
         </is>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>36.44</t>
+          <t>77.37</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>36.04</t>
+          <t>32.81</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>24.43</t>
+          <t>16.78</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>17.7</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>0.1446</t>
+          <t>0.1342</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
@@ -7946,8 +8122,16 @@
           <t>28.96</t>
         </is>
       </c>
-      <c r="BG8" t="inlineStr"/>
-      <c r="BH8" t="inlineStr"/>
+      <c r="BG8" t="inlineStr">
+        <is>
+          <t>L To R</t>
+        </is>
+      </c>
+      <c r="BH8" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
       <c r="BI8" t="inlineStr">
         <is>
           <t>American Family Field</t>
@@ -7961,12 +8145,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>592885</t>
+          <t>661388</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Christian Yelich</t>
+          <t>William Contreras</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -7986,12 +8170,12 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -8010,7 +8194,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>43.5</v>
+        <v>47.1</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -8024,40 +8208,40 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P9" t="n">
-        <v>38.2</v>
+        <v>39.5</v>
       </c>
       <c r="Q9" t="n">
         <v>34.3</v>
       </c>
       <c r="R9" t="n">
-        <v>27.6</v>
+        <v>41.1</v>
       </c>
       <c r="S9" t="n">
-        <v>71.7</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T9" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U9" t="n">
-        <v>25.3</v>
+        <v>37.8</v>
       </c>
       <c r="V9" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
@@ -8072,12 +8256,12 @@
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
+          <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>lineup projected / unconfirmed</t>
+          <t>RotoWire not confirmed</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -8099,7 +8283,7 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
@@ -8114,12 +8298,12 @@
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/24, 1 HR</t>
+          <t>Last 7 games: 6/24, 1 HR</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.9% barrel, 22.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 6.9% barrel, 22.0 HR allowed</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
@@ -8129,67 +8313,67 @@
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>9.81</t>
+          <t>7.87</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>43.95</t>
+          <t>45.42</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>89.29</t>
+          <t>90.54</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>100.9775</t>
+          <t>101.6393</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>0.4012</t>
+          <t>0.4266</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>0.1674</t>
+          <t>0.1702</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>0.3146</t>
+          <t>0.3322</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
         <is>
-          <t>73.23</t>
+          <t>73.41</t>
         </is>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>32.32</t>
+          <t>36.44</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>34.24</t>
+          <t>36.04</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>19.09</t>
+          <t>24.43</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>17.1</t>
+          <t>17.7</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>0.1565</t>
+          <t>0.1446</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
@@ -8222,8 +8406,16 @@
           <t>28.96</t>
         </is>
       </c>
-      <c r="BG9" t="inlineStr"/>
-      <c r="BH9" t="inlineStr"/>
+      <c r="BG9" t="inlineStr">
+        <is>
+          <t>L To R</t>
+        </is>
+      </c>
+      <c r="BH9" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
       <c r="BI9" t="inlineStr">
         <is>
           <t>American Family Field</t>
@@ -8262,7 +8454,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -8286,7 +8478,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -8310,7 +8502,7 @@
         <v>18.6</v>
       </c>
       <c r="R10" t="n">
-        <v>27.6</v>
+        <v>41.1</v>
       </c>
       <c r="S10" t="n">
         <v>71.7</v>
@@ -8498,8 +8690,16 @@
           <t>25.57</t>
         </is>
       </c>
-      <c r="BG10" t="inlineStr"/>
-      <c r="BH10" t="inlineStr"/>
+      <c r="BG10" t="inlineStr">
+        <is>
+          <t>L To R</t>
+        </is>
+      </c>
+      <c r="BH10" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
       <c r="BI10" t="inlineStr">
         <is>
           <t>American Family Field</t>
@@ -8538,7 +8738,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -8562,7 +8762,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>40.1</v>
+        <v>42.1</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -8586,7 +8786,7 @@
         <v>18.6</v>
       </c>
       <c r="R11" t="n">
-        <v>27.6</v>
+        <v>41.1</v>
       </c>
       <c r="S11" t="n">
         <v>88.7</v>
@@ -8774,8 +8974,16 @@
           <t>25.57</t>
         </is>
       </c>
-      <c r="BG11" t="inlineStr"/>
-      <c r="BH11" t="inlineStr"/>
+      <c r="BG11" t="inlineStr">
+        <is>
+          <t>L To R</t>
+        </is>
+      </c>
+      <c r="BH11" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
       <c r="BI11" t="inlineStr">
         <is>
           <t>American Family Field</t>
@@ -8814,7 +9022,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -8838,7 +9046,7 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -8862,7 +9070,7 @@
         <v>18.6</v>
       </c>
       <c r="R12" t="n">
-        <v>27.6</v>
+        <v>41.1</v>
       </c>
       <c r="S12" t="n">
         <v>90.40000000000001</v>
@@ -9050,8 +9258,16 @@
           <t>25.57</t>
         </is>
       </c>
-      <c r="BG12" t="inlineStr"/>
-      <c r="BH12" t="inlineStr"/>
+      <c r="BG12" t="inlineStr">
+        <is>
+          <t>L To R</t>
+        </is>
+      </c>
+      <c r="BH12" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
       <c r="BI12" t="inlineStr">
         <is>
           <t>American Family Field</t>
@@ -9065,12 +9281,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>800325</t>
+          <t>666152</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Luis Lara</t>
+          <t>David Hamilton</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -9090,12 +9306,12 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -9114,7 +9330,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>31.1</v>
+        <v>32.7</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -9128,65 +9344,57 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P13" t="n">
-        <v>16.6</v>
+        <v>11.1</v>
       </c>
       <c r="Q13" t="n">
-        <v>32.5</v>
+        <v>34.3</v>
       </c>
       <c r="R13" t="n">
-        <v>27.6</v>
+        <v>41.1</v>
       </c>
       <c r="S13" t="n">
-        <v>47.9</v>
+        <v>44.8</v>
       </c>
       <c r="T13" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="U13" t="n">
-        <v>5.1</v>
+        <v>23.7</v>
       </c>
       <c r="V13" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr"/>
+      <c r="X13" t="inlineStr"/>
+      <c r="Y13" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X13" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Y13" t="inlineStr">
+      <c r="Z13" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
+          <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>lineup projected / unconfirmed</t>
+          <t>not found on RotoWire</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD13" t="inlineStr"/>
@@ -9203,12 +9411,12 @@
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
@@ -9218,12 +9426,12 @@
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/26, 0 HR</t>
+          <t>Last 7 games: 5/18, 0 HR</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 6.9% barrel, 22.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.9% barrel, 22.0 HR allowed</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
@@ -9233,67 +9441,67 @@
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>3.4</t>
+          <t>4.18</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>41.5</t>
+          <t>27.87</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>86.74</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>98.8409</t>
+          <t>96.8019</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>0.331</t>
+          <t>0.3169</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
         <is>
-          <t>0.075</t>
+          <t>0.0967</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>0.293</t>
+          <t>0.2712</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
         <is>
-          <t>71.4</t>
+          <t>69.66</t>
         </is>
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>16.7</t>
+          <t>6.59</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>30.6</t>
+          <t>35.88</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>15.0</t>
+          <t>24.48</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>4.6</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>0.079</t>
+          <t>0.1042</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
@@ -9326,8 +9534,16 @@
           <t>28.96</t>
         </is>
       </c>
-      <c r="BG13" t="inlineStr"/>
-      <c r="BH13" t="inlineStr"/>
+      <c r="BG13" t="inlineStr">
+        <is>
+          <t>L To R</t>
+        </is>
+      </c>
+      <c r="BH13" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
       <c r="BI13" t="inlineStr">
         <is>
           <t>American Family Field</t>
@@ -9366,7 +9582,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -9390,7 +9606,7 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>30</v>
+        <v>32.6</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -9404,7 +9620,7 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>No major boost</t>
         </is>
       </c>
       <c r="P14" t="n">
@@ -9414,10 +9630,10 @@
         <v>34.3</v>
       </c>
       <c r="R14" t="n">
-        <v>27.6</v>
+        <v>41.1</v>
       </c>
       <c r="S14" t="n">
-        <v>59.8</v>
+        <v>64.3</v>
       </c>
       <c r="T14" t="n">
         <v>50</v>
@@ -9427,14 +9643,14 @@
       </c>
       <c r="V14" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="X14" t="inlineStr">
         <is>
           <t>7</t>
@@ -9452,12 +9668,12 @@
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
+          <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>lineup projected / unconfirmed</t>
+          <t>RotoWire not confirmed</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
@@ -9602,8 +9818,16 @@
           <t>28.96</t>
         </is>
       </c>
-      <c r="BG14" t="inlineStr"/>
-      <c r="BH14" t="inlineStr"/>
+      <c r="BG14" t="inlineStr">
+        <is>
+          <t>L To R</t>
+        </is>
+      </c>
+      <c r="BH14" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
       <c r="BI14" t="inlineStr">
         <is>
           <t>American Family Field</t>
@@ -9617,12 +9841,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>687401</t>
+          <t>686217</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Joey Ortiz</t>
+          <t>Sal Frelick</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -9642,12 +9866,12 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -9666,7 +9890,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>29.3</v>
+        <v>31.6</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -9680,60 +9904,52 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P15" t="n">
-        <v>17.1</v>
+        <v>5.4</v>
       </c>
       <c r="Q15" t="n">
         <v>34.3</v>
       </c>
       <c r="R15" t="n">
-        <v>27.6</v>
+        <v>41.1</v>
       </c>
       <c r="S15" t="n">
-        <v>40.2</v>
+        <v>52.4</v>
       </c>
       <c r="T15" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U15" t="n">
-        <v>22.4</v>
+        <v>17.3</v>
       </c>
       <c r="V15" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr"/>
+      <c r="X15" t="inlineStr"/>
+      <c r="Y15" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X15" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="Y15" t="inlineStr">
+      <c r="Z15" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
+          <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>lineup projected / unconfirmed</t>
+          <t>not found on RotoWire</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
@@ -9755,12 +9971,12 @@
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>17</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
@@ -9770,12 +9986,12 @@
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>Last 7 games: 7/26, 0 HR</t>
+          <t>Last 7 games: 4/17, 0 HR</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 6.9% barrel, 22.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.9% barrel, 22.0 HR allowed</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
@@ -9785,67 +10001,67 @@
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>3.7</t>
+          <t>2.54</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>36.16</t>
+          <t>26.98</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>87.91</t>
+          <t>85.64</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>99.2209</t>
+          <t>96.2217</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>0.3403</t>
+          <t>0.3285</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
         <is>
-          <t>0.0967</t>
+          <t>0.0826</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>0.2904</t>
+          <t>0.2864</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>68.24</t>
         </is>
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>30.57</t>
+          <t>3.76</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>31.91</t>
+          <t>39.46</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>19.68</t>
+          <t>20.9</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>6.4</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>0.1185</t>
+          <t>0.0974</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
@@ -9878,8 +10094,16 @@
           <t>28.96</t>
         </is>
       </c>
-      <c r="BG15" t="inlineStr"/>
-      <c r="BH15" t="inlineStr"/>
+      <c r="BG15" t="inlineStr">
+        <is>
+          <t>L To R</t>
+        </is>
+      </c>
+      <c r="BH15" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
       <c r="BI15" t="inlineStr">
         <is>
           <t>American Family Field</t>
@@ -9918,7 +10142,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -9942,7 +10166,7 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>28.6</v>
+        <v>30.6</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -9966,7 +10190,7 @@
         <v>18.6</v>
       </c>
       <c r="R16" t="n">
-        <v>27.6</v>
+        <v>41.1</v>
       </c>
       <c r="S16" t="n">
         <v>47.9</v>
@@ -10154,8 +10378,16 @@
           <t>25.57</t>
         </is>
       </c>
-      <c r="BG16" t="inlineStr"/>
-      <c r="BH16" t="inlineStr"/>
+      <c r="BG16" t="inlineStr">
+        <is>
+          <t>L To R</t>
+        </is>
+      </c>
+      <c r="BH16" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
       <c r="BI16" t="inlineStr">
         <is>
           <t>American Family Field</t>
@@ -10194,7 +10426,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -10218,7 +10450,7 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>28.5</v>
+        <v>30.5</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -10242,7 +10474,7 @@
         <v>18.6</v>
       </c>
       <c r="R17" t="n">
-        <v>27.6</v>
+        <v>41.1</v>
       </c>
       <c r="S17" t="n">
         <v>59.8</v>
@@ -10430,8 +10662,16 @@
           <t>25.57</t>
         </is>
       </c>
-      <c r="BG17" t="inlineStr"/>
-      <c r="BH17" t="inlineStr"/>
+      <c r="BG17" t="inlineStr">
+        <is>
+          <t>L To R</t>
+        </is>
+      </c>
+      <c r="BH17" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
       <c r="BI17" t="inlineStr">
         <is>
           <t>American Family Field</t>
@@ -10470,7 +10710,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -10494,7 +10734,7 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>28.1</v>
+        <v>30.1</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -10518,7 +10758,7 @@
         <v>18.6</v>
       </c>
       <c r="R18" t="n">
-        <v>27.6</v>
+        <v>41.1</v>
       </c>
       <c r="S18" t="n">
         <v>81.90000000000001</v>
@@ -10706,8 +10946,16 @@
           <t>25.57</t>
         </is>
       </c>
-      <c r="BG18" t="inlineStr"/>
-      <c r="BH18" t="inlineStr"/>
+      <c r="BG18" t="inlineStr">
+        <is>
+          <t>L To R</t>
+        </is>
+      </c>
+      <c r="BH18" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
       <c r="BI18" t="inlineStr">
         <is>
           <t>American Family Field</t>
@@ -10746,7 +10994,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -10770,7 +11018,7 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>23.9</v>
+        <v>25.9</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -10794,7 +11042,7 @@
         <v>17.3</v>
       </c>
       <c r="R19" t="n">
-        <v>27.6</v>
+        <v>41.1</v>
       </c>
       <c r="S19" t="n">
         <v>40.2</v>
@@ -10982,8 +11230,16 @@
           <t>25.57</t>
         </is>
       </c>
-      <c r="BG19" t="inlineStr"/>
-      <c r="BH19" t="inlineStr"/>
+      <c r="BG19" t="inlineStr">
+        <is>
+          <t>L To R</t>
+        </is>
+      </c>
+      <c r="BH19" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
       <c r="BI19" t="inlineStr">
         <is>
           <t>American Family Field</t>

--- a/outputs/daily/hr_rankings_2026-10-23.xlsx
+++ b/outputs/daily/hr_rankings_2026-10-23.xlsx
@@ -826,34 +826,30 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 2 vs RotoWire 3</t>
-        </is>
-      </c>
+      <c r="AB2" t="inlineStr"/>
       <c r="AC2" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -1110,34 +1106,30 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB3" t="inlineStr"/>
       <c r="AC3" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -1333,7 +1325,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -1352,7 +1344,7 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>50.4</v>
+        <v>50.8</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -1366,7 +1358,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
+          <t>Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P4" t="n">
@@ -1379,7 +1371,7 @@
         <v>41.1</v>
       </c>
       <c r="S4" t="n">
-        <v>92.09999999999999</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T4" t="n">
         <v>50</v>
@@ -1389,39 +1381,35 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr"/>
       <c r="AC4" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -1587,24 +1575,24 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>592885</t>
+          <t>666018</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Christian Yelich</t>
+          <t>Jonathan Aranda</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
           <t>MIL</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>TB</t>
-        </is>
-      </c>
       <c r="F5" t="inlineStr">
         <is>
           <t>2026-10-24T00:00:00Z</t>
@@ -1617,17 +1605,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Nick Martinez</t>
+          <t>Jacob Misiorowski</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>607259</t>
+          <t>694819</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1636,7 +1624,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>49</v>
+        <v>49.4</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -1650,26 +1638,26 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P5" t="n">
-        <v>38.2</v>
+        <v>48.9</v>
       </c>
       <c r="Q5" t="n">
-        <v>34.3</v>
+        <v>18.6</v>
       </c>
       <c r="R5" t="n">
         <v>41.1</v>
       </c>
       <c r="S5" t="n">
-        <v>96.59999999999999</v>
+        <v>100</v>
       </c>
       <c r="T5" t="n">
         <v>80</v>
       </c>
       <c r="U5" t="n">
-        <v>25.3</v>
+        <v>28.9</v>
       </c>
       <c r="V5" t="inlineStr">
         <is>
@@ -1678,34 +1666,30 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 3 vs RotoWire 6</t>
-        </is>
-      </c>
+      <c r="AB5" t="inlineStr"/>
       <c r="AC5" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -1730,7 +1714,7 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
@@ -1740,12 +1724,12 @@
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/24, 1 HR</t>
+          <t>Last 7 games: 4/21, 1 HR</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.9% barrel, 22.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 4.9% barrel, 12.2 HR allowed</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
@@ -1755,97 +1739,97 @@
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>9.81</t>
+          <t>10.8</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>43.95</t>
+          <t>48.55</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>89.29</t>
+          <t>91.67</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>100.9775</t>
+          <t>101.2282</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>0.4012</t>
+          <t>0.4611</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>0.1674</t>
+          <t>0.196</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>0.3146</t>
+          <t>0.3547</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>73.23</t>
+          <t>70.36</t>
         </is>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>32.32</t>
+          <t>13.11</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>34.24</t>
+          <t>33.13</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>19.09</t>
+          <t>30.13</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>17.1</t>
+          <t>19.6</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>0.1565</t>
+          <t>0.1639</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>6.86</t>
+          <t>4.89</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>33.38</t>
+          <t>34.56</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>87.39</t>
+          <t>87.74</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>0.4114</t>
+          <t>0.2817</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
-          <t>0.1502</t>
+          <t>0.0996</t>
         </is>
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>28.96</t>
+          <t>25.57</t>
         </is>
       </c>
       <c r="BG5" t="inlineStr">
@@ -1871,12 +1855,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>668930</t>
+          <t>592885</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Brice Turang</t>
+          <t>Christian Yelich</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1901,7 +1885,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1934,11 +1918,11 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P6" t="n">
-        <v>36.6</v>
+        <v>38.2</v>
       </c>
       <c r="Q6" t="n">
         <v>34.3</v>
@@ -1947,13 +1931,13 @@
         <v>41.1</v>
       </c>
       <c r="S6" t="n">
-        <v>86.40000000000001</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T6" t="n">
         <v>80</v>
       </c>
       <c r="U6" t="n">
-        <v>65.2</v>
+        <v>25.3</v>
       </c>
       <c r="V6" t="inlineStr">
         <is>
@@ -1962,34 +1946,30 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 5 vs RotoWire 2</t>
-        </is>
-      </c>
+      <c r="AB6" t="inlineStr"/>
       <c r="AC6" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -2009,22 +1989,22 @@
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 4/24, 1 HR</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
@@ -2039,67 +2019,67 @@
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>7.79</t>
+          <t>9.81</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>43.34</t>
+          <t>43.95</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>90.54</t>
+          <t>89.29</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>100.4264</t>
+          <t>100.9775</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>0.4283</t>
+          <t>0.4012</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>0.1712</t>
+          <t>0.1674</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>0.3413</t>
+          <t>0.3146</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>70.25</t>
+          <t>73.23</t>
         </is>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>13.2</t>
+          <t>32.32</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>28.21</t>
+          <t>34.24</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>23.43</t>
+          <t>19.09</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>20.1</t>
+          <t>17.1</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>0.1715</t>
+          <t>0.1565</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
@@ -2155,24 +2135,24 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>666018</t>
+          <t>668930</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Jonathan Aranda</t>
+          <t>Brice Turang</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
+          <t>MIL</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
           <t>TB</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>MIL</t>
-        </is>
-      </c>
       <c r="F7" t="inlineStr">
         <is>
           <t>2026-10-24T00:00:00Z</t>
@@ -2185,17 +2165,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Jacob Misiorowski</t>
+          <t>Nick Martinez</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>694819</t>
+          <t>607259</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -2204,7 +2184,7 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>48.8</v>
+        <v>49</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -2218,62 +2198,58 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P7" t="n">
-        <v>48.9</v>
+        <v>36.6</v>
       </c>
       <c r="Q7" t="n">
-        <v>18.6</v>
+        <v>34.3</v>
       </c>
       <c r="R7" t="n">
         <v>41.1</v>
       </c>
       <c r="S7" t="n">
-        <v>95.5</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T7" t="n">
         <v>80</v>
       </c>
       <c r="U7" t="n">
-        <v>28.9</v>
+        <v>65.2</v>
       </c>
       <c r="V7" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr"/>
       <c r="AC7" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -2293,27 +2269,27 @@
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/21, 1 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 4.9% barrel, 12.2 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.9% barrel, 22.0 HR allowed</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
@@ -2323,97 +2299,97 @@
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>10.8</t>
+          <t>7.79</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>48.55</t>
+          <t>43.34</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>91.67</t>
+          <t>90.54</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>101.2282</t>
+          <t>100.4264</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>0.4611</t>
+          <t>0.4283</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>0.196</t>
+          <t>0.1712</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>0.3547</t>
+          <t>0.3413</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>70.36</t>
+          <t>70.25</t>
         </is>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>13.11</t>
+          <t>13.2</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>33.13</t>
+          <t>28.21</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>30.13</t>
+          <t>23.43</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>19.6</t>
+          <t>20.1</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>0.1639</t>
+          <t>0.1715</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>4.89</t>
+          <t>6.86</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>34.56</t>
+          <t>33.38</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>87.74</t>
+          <t>87.39</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>0.2817</t>
+          <t>0.4114</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
-          <t>0.0996</t>
+          <t>0.1502</t>
         </is>
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>25.57</t>
+          <t>28.96</t>
         </is>
       </c>
       <c r="BG7" t="inlineStr">
@@ -2530,34 +2506,30 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 6 vs RotoWire 5</t>
-        </is>
-      </c>
+      <c r="AB8" t="inlineStr"/>
       <c r="AC8" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -2814,34 +2786,30 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB9" t="inlineStr"/>
       <c r="AC9" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -3012,7 +2980,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Victor Mesa</t>
+          <t>Victor Mesa Jr.</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -3037,7 +3005,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -3056,7 +3024,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -3070,7 +3038,7 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P10" t="n">
@@ -3083,7 +3051,7 @@
         <v>41.1</v>
       </c>
       <c r="S10" t="n">
-        <v>71.7</v>
+        <v>64.3</v>
       </c>
       <c r="T10" t="n">
         <v>80</v>
@@ -3093,39 +3061,35 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr"/>
       <c r="AC10" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -3296,7 +3260,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Yandy Diaz</t>
+          <t>Yandy Díaz</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -3340,7 +3304,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>42.1</v>
+        <v>42.7</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -3354,7 +3318,7 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P11" t="n">
@@ -3367,7 +3331,7 @@
         <v>41.1</v>
       </c>
       <c r="S11" t="n">
-        <v>88.7</v>
+        <v>93.2</v>
       </c>
       <c r="T11" t="n">
         <v>50</v>
@@ -3377,39 +3341,35 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr"/>
       <c r="AC11" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -3605,7 +3565,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -3624,7 +3584,7 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>34</v>
+        <v>33.5</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -3638,7 +3598,7 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P12" t="n">
@@ -3651,7 +3611,7 @@
         <v>41.1</v>
       </c>
       <c r="S12" t="n">
-        <v>90.40000000000001</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T12" t="n">
         <v>80</v>
@@ -3661,39 +3621,35 @@
       </c>
       <c r="V12" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr"/>
       <c r="AC12" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -3859,24 +3815,24 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>666152</t>
+          <t>676356</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>David Hamilton</t>
+          <t>Jonny DeLuca</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
           <t>MIL</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>TB</t>
-        </is>
-      </c>
       <c r="F13" t="inlineStr">
         <is>
           <t>2026-10-24T00:00:00Z</t>
@@ -3889,17 +3845,17 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Nick Martinez</t>
+          <t>Jacob Misiorowski</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>607259</t>
+          <t>694819</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -3908,7 +3864,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>32.7</v>
+        <v>32.8</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -3922,54 +3878,58 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Platoon Edge</t>
+          <t>Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P13" t="n">
-        <v>11.1</v>
+        <v>10.6</v>
       </c>
       <c r="Q13" t="n">
-        <v>34.3</v>
+        <v>18.6</v>
       </c>
       <c r="R13" t="n">
         <v>41.1</v>
       </c>
       <c r="S13" t="n">
-        <v>44.8</v>
+        <v>76.2</v>
       </c>
       <c r="T13" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U13" t="n">
-        <v>23.7</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="V13" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W13" t="inlineStr"/>
-      <c r="X13" t="inlineStr"/>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="Y13" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>not found on RotoWire</t>
-        </is>
-      </c>
+      <c r="AB13" t="inlineStr"/>
       <c r="AC13" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -3989,27 +3949,27 @@
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/18, 0 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.9% barrel, 22.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 4.9% barrel, 12.2 HR allowed</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
@@ -4019,97 +3979,97 @@
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>4.18</t>
+          <t>3.21</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>27.87</t>
+          <t>30.68</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>86.74</t>
+          <t>85.74</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>96.8019</t>
+          <t>97.7063</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>0.3169</t>
+          <t>0.3262</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
         <is>
-          <t>0.0967</t>
+          <t>0.0879</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>0.2712</t>
+          <t>0.2628</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
         <is>
-          <t>69.66</t>
+          <t>72.75</t>
         </is>
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>6.59</t>
+          <t>28.03</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>35.88</t>
+          <t>45.6</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>24.48</t>
+          <t>22.55</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>4.6</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>0.1042</t>
+          <t>0.151</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>6.86</t>
+          <t>4.89</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>33.38</t>
+          <t>34.56</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>87.39</t>
+          <t>87.74</t>
         </is>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
-          <t>0.4114</t>
+          <t>0.2817</t>
         </is>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
-          <t>0.1502</t>
+          <t>0.0996</t>
         </is>
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>28.96</t>
+          <t>25.57</t>
         </is>
       </c>
       <c r="BG13" t="inlineStr">
@@ -4135,12 +4095,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>806198</t>
+          <t>666152</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Cooper Pratt</t>
+          <t>David Hamilton</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -4165,7 +4125,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -4184,7 +4144,7 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>32.6</v>
+        <v>32.7</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -4198,11 +4158,11 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>No major boost</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P14" t="n">
-        <v>10.5</v>
+        <v>11.1</v>
       </c>
       <c r="Q14" t="n">
         <v>34.3</v>
@@ -4211,13 +4171,13 @@
         <v>41.1</v>
       </c>
       <c r="S14" t="n">
-        <v>64.3</v>
+        <v>44.8</v>
       </c>
       <c r="T14" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U14" t="n">
-        <v>24.9</v>
+        <v>23.7</v>
       </c>
       <c r="V14" t="inlineStr">
         <is>
@@ -4226,37 +4186,33 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X14" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Y14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB14" t="inlineStr"/>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD14" t="inlineStr"/>
@@ -4273,12 +4229,12 @@
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
@@ -4288,12 +4244,12 @@
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/21, 0 HR</t>
+          <t>Last 7 games: 5/18, 0 HR</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 6.9% barrel, 22.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.9% barrel, 22.0 HR allowed</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
@@ -4303,67 +4259,67 @@
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>3.2</t>
+          <t>4.18</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>27.4</t>
+          <t>27.87</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>86.74</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>96.5693</t>
+          <t>96.8019</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>0.362</t>
+          <t>0.3169</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
         <is>
-          <t>0.096</t>
+          <t>0.0967</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>0.315</t>
+          <t>0.2712</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
         <is>
-          <t>69.9</t>
+          <t>69.66</t>
         </is>
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>8.6</t>
+          <t>6.59</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>33.2</t>
+          <t>35.88</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>21.1</t>
+          <t>24.48</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>4.6</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>0.087</t>
+          <t>0.1042</t>
         </is>
       </c>
       <c r="BA14" t="inlineStr">
@@ -4419,12 +4375,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>686217</t>
+          <t>806198</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Sal Frelick</t>
+          <t>Cooper Pratt</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -4449,7 +4405,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -4468,7 +4424,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>31.6</v>
+        <v>32.6</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -4482,11 +4438,11 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Platoon Edge</t>
+          <t>No major boost</t>
         </is>
       </c>
       <c r="P15" t="n">
-        <v>5.4</v>
+        <v>10.5</v>
       </c>
       <c r="Q15" t="n">
         <v>34.3</v>
@@ -4495,44 +4451,48 @@
         <v>41.1</v>
       </c>
       <c r="S15" t="n">
-        <v>52.4</v>
+        <v>64.3</v>
       </c>
       <c r="T15" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U15" t="n">
-        <v>17.3</v>
+        <v>24.9</v>
       </c>
       <c r="V15" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W15" t="inlineStr"/>
-      <c r="X15" t="inlineStr"/>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="Y15" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>not found on RotoWire</t>
-        </is>
-      </c>
+      <c r="AB15" t="inlineStr"/>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AD15" t="inlineStr"/>
@@ -4549,12 +4509,12 @@
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
@@ -4564,12 +4524,12 @@
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/17, 0 HR</t>
+          <t>Last 7 games: 6/21, 0 HR</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.9% barrel, 22.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 6.9% barrel, 22.0 HR allowed</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
@@ -4579,67 +4539,67 @@
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>2.54</t>
+          <t>3.2</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>26.98</t>
+          <t>27.4</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>85.64</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>96.2217</t>
+          <t>96.5693</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>0.3285</t>
+          <t>0.362</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
         <is>
-          <t>0.0826</t>
+          <t>0.096</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>0.2864</t>
+          <t>0.315</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
         <is>
-          <t>68.24</t>
+          <t>69.9</t>
         </is>
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>3.76</t>
+          <t>8.6</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>39.46</t>
+          <t>33.2</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>20.9</t>
+          <t>21.1</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>6.4</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>0.0974</t>
+          <t>0.087</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
@@ -4695,12 +4655,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>680700</t>
+          <t>802415</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Richie Palacios</t>
+          <t>Chandler Simpson</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -4725,7 +4685,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -4744,7 +4704,7 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>30.6</v>
+        <v>32.2</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -4758,11 +4718,11 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P16" t="n">
-        <v>15.4</v>
+        <v>0.2</v>
       </c>
       <c r="Q16" t="n">
         <v>18.6</v>
@@ -4771,49 +4731,45 @@
         <v>41.1</v>
       </c>
       <c r="S16" t="n">
-        <v>47.9</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T16" t="n">
         <v>80</v>
       </c>
       <c r="U16" t="n">
-        <v>19.5</v>
+        <v>15.3</v>
       </c>
       <c r="V16" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X16" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Y16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr"/>
       <c r="AC16" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -4833,12 +4789,12 @@
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
@@ -4848,7 +4804,7 @@
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/20, 0 HR</t>
+          <t>Last 7 games: 6/27, 0 HR</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
@@ -4863,67 +4819,67 @@
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>4.57</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>33.39</t>
+          <t>14.71</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>87.31</t>
+          <t>83.88</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>97.1084</t>
+          <t>92.929</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>0.3655</t>
+          <t>0.3087</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
         <is>
-          <t>0.1018</t>
+          <t>0.0382</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>0.3213</t>
+          <t>0.2732</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
         <is>
-          <t>68.91</t>
+          <t>64.8</t>
         </is>
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>3.94</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>37.09</t>
+          <t>28.27</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>20.98</t>
+          <t>12.51</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>7.3</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>0.133</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
@@ -4979,24 +4935,24 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>676356</t>
+          <t>686217</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Jonny DeLuca</t>
+          <t>Sal Frelick</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
+          <t>MIL</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
           <t>TB</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>MIL</t>
-        </is>
-      </c>
       <c r="F17" t="inlineStr">
         <is>
           <t>2026-10-24T00:00:00Z</t>
@@ -5009,17 +4965,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Jacob Misiorowski</t>
+          <t>Nick Martinez</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>694819</t>
+          <t>607259</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -5028,7 +4984,7 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>30.5</v>
+        <v>31.6</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -5042,62 +4998,58 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Projected Lineup, Hot Hitter/Streak</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P17" t="n">
-        <v>10.6</v>
+        <v>5.4</v>
       </c>
       <c r="Q17" t="n">
-        <v>18.6</v>
+        <v>34.3</v>
       </c>
       <c r="R17" t="n">
         <v>41.1</v>
       </c>
       <c r="S17" t="n">
-        <v>59.8</v>
+        <v>52.4</v>
       </c>
       <c r="T17" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U17" t="n">
-        <v>70.59999999999999</v>
+        <v>17.3</v>
       </c>
       <c r="V17" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X17" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Y17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr"/>
       <c r="AC17" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -5117,27 +5069,27 @@
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>17</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 4/17, 0 HR</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 4.9% barrel, 12.2 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.9% barrel, 22.0 HR allowed</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
@@ -5147,97 +5099,97 @@
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>3.21</t>
+          <t>2.54</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>30.68</t>
+          <t>26.98</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>85.74</t>
+          <t>85.64</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>97.7063</t>
+          <t>96.2217</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>0.3262</t>
+          <t>0.3285</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
         <is>
-          <t>0.0879</t>
+          <t>0.0826</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>0.2628</t>
+          <t>0.2864</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
         <is>
-          <t>72.75</t>
+          <t>68.24</t>
         </is>
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>28.03</t>
+          <t>3.76</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>45.6</t>
+          <t>39.46</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>22.55</t>
+          <t>20.9</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>6.4</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>0.151</t>
+          <t>0.0974</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>4.89</t>
+          <t>6.86</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>34.56</t>
+          <t>33.38</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>87.74</t>
+          <t>87.39</t>
         </is>
       </c>
       <c r="BD17" t="inlineStr">
         <is>
-          <t>0.2817</t>
+          <t>0.4114</t>
         </is>
       </c>
       <c r="BE17" t="inlineStr">
         <is>
-          <t>0.0996</t>
+          <t>0.1502</t>
         </is>
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>25.57</t>
+          <t>28.96</t>
         </is>
       </c>
       <c r="BG17" t="inlineStr">
@@ -5263,12 +5215,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>802415</t>
+          <t>670764</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Chandler Simpson</t>
+          <t>Taylor Walls</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -5293,7 +5245,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -5312,7 +5264,7 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>30.1</v>
+        <v>26.5</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -5326,62 +5278,58 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P18" t="n">
-        <v>0.2</v>
+        <v>5.6</v>
       </c>
       <c r="Q18" t="n">
-        <v>18.6</v>
+        <v>17.3</v>
       </c>
       <c r="R18" t="n">
         <v>41.1</v>
       </c>
       <c r="S18" t="n">
-        <v>81.90000000000001</v>
+        <v>44.8</v>
       </c>
       <c r="T18" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="U18" t="n">
-        <v>15.3</v>
+        <v>27</v>
       </c>
       <c r="V18" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X18" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr"/>
       <c r="AC18" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -5406,7 +5354,7 @@
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
@@ -5416,12 +5364,12 @@
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/27, 0 HR</t>
+          <t>Last 7 games: 6/20, 0 HR</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 4.9% barrel, 12.2 HR allowed</t>
+          <t>switch hitter; pitcher baseline 4.9% barrel, 12.2 HR allowed</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
@@ -5431,67 +5379,67 @@
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>14.71</t>
+          <t>23.25</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>83.88</t>
+          <t>86.02</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>92.929</t>
+          <t>95.5424</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>0.3087</t>
+          <t>0.2754</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
         <is>
-          <t>0.0382</t>
+          <t>0.0794</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>0.2732</t>
+          <t>0.254</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
         <is>
-          <t>64.8</t>
+          <t>68.28</t>
         </is>
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>1.92</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>28.27</t>
+          <t>38.82</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>12.51</t>
+          <t>28.77</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.6</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.0829</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
@@ -5547,12 +5495,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>670764</t>
+          <t>810938</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Taylor Walls</t>
+          <t>Ben Williamson</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -5577,7 +5525,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -5596,7 +5544,7 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>25.9</v>
+        <v>26.3</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -5610,62 +5558,58 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>No major boost</t>
         </is>
       </c>
       <c r="P19" t="n">
-        <v>5.6</v>
+        <v>11.6</v>
       </c>
       <c r="Q19" t="n">
-        <v>17.3</v>
+        <v>18.6</v>
       </c>
       <c r="R19" t="n">
         <v>41.1</v>
       </c>
       <c r="S19" t="n">
-        <v>40.2</v>
+        <v>52.4</v>
       </c>
       <c r="T19" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="U19" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="V19" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X19" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="Y19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr"/>
       <c r="AC19" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -5685,12 +5629,12 @@
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
@@ -5700,12 +5644,12 @@
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/20, 0 HR</t>
+          <t>Last 7 games: 2/19, 0 HR</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 4.9% barrel, 12.2 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 4.9% barrel, 12.2 HR allowed</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
@@ -5715,67 +5659,67 @@
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>2.32</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>23.25</t>
+          <t>35.39</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>86.02</t>
+          <t>87.6</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>95.5424</t>
+          <t>98.4446</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>0.2754</t>
+          <t>0.3241</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
         <is>
-          <t>0.0794</t>
+          <t>0.0789</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>0.254</t>
+          <t>0.2809</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
         <is>
-          <t>68.28</t>
+          <t>69.49</t>
         </is>
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>1.92</t>
+          <t>10.53</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>38.82</t>
+          <t>27.55</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>28.77</t>
+          <t>14.95</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>2.6</t>
+          <t>2.4</t>
         </is>
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>0.0829</t>
+          <t>0.0731</t>
         </is>
       </c>
       <c r="BA19" t="inlineStr">
@@ -6248,34 +6192,30 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 2 vs RotoWire 3</t>
-        </is>
-      </c>
+      <c r="AB2" t="inlineStr"/>
       <c r="AC2" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -6532,34 +6472,30 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB3" t="inlineStr"/>
       <c r="AC3" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -6755,7 +6691,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -6774,7 +6710,7 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>50.4</v>
+        <v>50.8</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -6788,7 +6724,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
+          <t>Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P4" t="n">
@@ -6801,7 +6737,7 @@
         <v>41.1</v>
       </c>
       <c r="S4" t="n">
-        <v>92.09999999999999</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T4" t="n">
         <v>50</v>
@@ -6811,39 +6747,35 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr"/>
       <c r="AC4" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -7009,24 +6941,24 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>592885</t>
+          <t>666018</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Christian Yelich</t>
+          <t>Jonathan Aranda</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
           <t>MIL</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>TB</t>
-        </is>
-      </c>
       <c r="F5" t="inlineStr">
         <is>
           <t>2026-10-24T00:00:00Z</t>
@@ -7039,17 +6971,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Nick Martinez</t>
+          <t>Jacob Misiorowski</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>607259</t>
+          <t>694819</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -7058,7 +6990,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>49</v>
+        <v>49.4</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -7072,26 +7004,26 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P5" t="n">
-        <v>38.2</v>
+        <v>48.9</v>
       </c>
       <c r="Q5" t="n">
-        <v>34.3</v>
+        <v>18.6</v>
       </c>
       <c r="R5" t="n">
         <v>41.1</v>
       </c>
       <c r="S5" t="n">
-        <v>96.59999999999999</v>
+        <v>100</v>
       </c>
       <c r="T5" t="n">
         <v>80</v>
       </c>
       <c r="U5" t="n">
-        <v>25.3</v>
+        <v>28.9</v>
       </c>
       <c r="V5" t="inlineStr">
         <is>
@@ -7100,34 +7032,30 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 3 vs RotoWire 6</t>
-        </is>
-      </c>
+      <c r="AB5" t="inlineStr"/>
       <c r="AC5" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -7152,7 +7080,7 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
@@ -7162,12 +7090,12 @@
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/24, 1 HR</t>
+          <t>Last 7 games: 4/21, 1 HR</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.9% barrel, 22.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 4.9% barrel, 12.2 HR allowed</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
@@ -7177,97 +7105,97 @@
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>9.81</t>
+          <t>10.8</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>43.95</t>
+          <t>48.55</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>89.29</t>
+          <t>91.67</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>100.9775</t>
+          <t>101.2282</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>0.4012</t>
+          <t>0.4611</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>0.1674</t>
+          <t>0.196</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>0.3146</t>
+          <t>0.3547</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>73.23</t>
+          <t>70.36</t>
         </is>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>32.32</t>
+          <t>13.11</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>34.24</t>
+          <t>33.13</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>19.09</t>
+          <t>30.13</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>17.1</t>
+          <t>19.6</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>0.1565</t>
+          <t>0.1639</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>6.86</t>
+          <t>4.89</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>33.38</t>
+          <t>34.56</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>87.39</t>
+          <t>87.74</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>0.4114</t>
+          <t>0.2817</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
-          <t>0.1502</t>
+          <t>0.0996</t>
         </is>
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>28.96</t>
+          <t>25.57</t>
         </is>
       </c>
       <c r="BG5" t="inlineStr">
@@ -7293,12 +7221,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>668930</t>
+          <t>592885</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Brice Turang</t>
+          <t>Christian Yelich</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -7323,7 +7251,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -7356,11 +7284,11 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P6" t="n">
-        <v>36.6</v>
+        <v>38.2</v>
       </c>
       <c r="Q6" t="n">
         <v>34.3</v>
@@ -7369,13 +7297,13 @@
         <v>41.1</v>
       </c>
       <c r="S6" t="n">
-        <v>86.40000000000001</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T6" t="n">
         <v>80</v>
       </c>
       <c r="U6" t="n">
-        <v>65.2</v>
+        <v>25.3</v>
       </c>
       <c r="V6" t="inlineStr">
         <is>
@@ -7384,34 +7312,30 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 5 vs RotoWire 2</t>
-        </is>
-      </c>
+      <c r="AB6" t="inlineStr"/>
       <c r="AC6" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -7431,22 +7355,22 @@
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 4/24, 1 HR</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
@@ -7461,67 +7385,67 @@
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>7.79</t>
+          <t>9.81</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>43.34</t>
+          <t>43.95</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>90.54</t>
+          <t>89.29</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>100.4264</t>
+          <t>100.9775</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>0.4283</t>
+          <t>0.4012</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>0.1712</t>
+          <t>0.1674</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>0.3413</t>
+          <t>0.3146</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>70.25</t>
+          <t>73.23</t>
         </is>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>13.2</t>
+          <t>32.32</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>28.21</t>
+          <t>34.24</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>23.43</t>
+          <t>19.09</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>20.1</t>
+          <t>17.1</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>0.1715</t>
+          <t>0.1565</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
@@ -7577,24 +7501,24 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>666018</t>
+          <t>668930</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Jonathan Aranda</t>
+          <t>Brice Turang</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
+          <t>MIL</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
           <t>TB</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>MIL</t>
-        </is>
-      </c>
       <c r="F7" t="inlineStr">
         <is>
           <t>2026-10-24T00:00:00Z</t>
@@ -7607,17 +7531,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Jacob Misiorowski</t>
+          <t>Nick Martinez</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>694819</t>
+          <t>607259</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -7626,7 +7550,7 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>48.8</v>
+        <v>49</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -7640,62 +7564,58 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P7" t="n">
-        <v>48.9</v>
+        <v>36.6</v>
       </c>
       <c r="Q7" t="n">
-        <v>18.6</v>
+        <v>34.3</v>
       </c>
       <c r="R7" t="n">
         <v>41.1</v>
       </c>
       <c r="S7" t="n">
-        <v>95.5</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T7" t="n">
         <v>80</v>
       </c>
       <c r="U7" t="n">
-        <v>28.9</v>
+        <v>65.2</v>
       </c>
       <c r="V7" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr"/>
       <c r="AC7" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -7715,27 +7635,27 @@
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/21, 1 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 4.9% barrel, 12.2 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.9% barrel, 22.0 HR allowed</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
@@ -7745,97 +7665,97 @@
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>10.8</t>
+          <t>7.79</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>48.55</t>
+          <t>43.34</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>91.67</t>
+          <t>90.54</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>101.2282</t>
+          <t>100.4264</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>0.4611</t>
+          <t>0.4283</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>0.196</t>
+          <t>0.1712</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>0.3547</t>
+          <t>0.3413</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>70.36</t>
+          <t>70.25</t>
         </is>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>13.11</t>
+          <t>13.2</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>33.13</t>
+          <t>28.21</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>30.13</t>
+          <t>23.43</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>19.6</t>
+          <t>20.1</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>0.1639</t>
+          <t>0.1715</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>4.89</t>
+          <t>6.86</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>34.56</t>
+          <t>33.38</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>87.74</t>
+          <t>87.39</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>0.2817</t>
+          <t>0.4114</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
-          <t>0.0996</t>
+          <t>0.1502</t>
         </is>
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>25.57</t>
+          <t>28.96</t>
         </is>
       </c>
       <c r="BG7" t="inlineStr">
@@ -7952,34 +7872,30 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 6 vs RotoWire 5</t>
-        </is>
-      </c>
+      <c r="AB8" t="inlineStr"/>
       <c r="AC8" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -8236,34 +8152,30 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB9" t="inlineStr"/>
       <c r="AC9" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -8434,7 +8346,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Victor Mesa</t>
+          <t>Victor Mesa Jr.</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -8459,7 +8371,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -8478,7 +8390,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -8492,7 +8404,7 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P10" t="n">
@@ -8505,7 +8417,7 @@
         <v>41.1</v>
       </c>
       <c r="S10" t="n">
-        <v>71.7</v>
+        <v>64.3</v>
       </c>
       <c r="T10" t="n">
         <v>80</v>
@@ -8515,39 +8427,35 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr"/>
       <c r="AC10" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -8718,7 +8626,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Yandy Diaz</t>
+          <t>Yandy Díaz</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -8762,7 +8670,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>42.1</v>
+        <v>42.7</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -8776,7 +8684,7 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P11" t="n">
@@ -8789,7 +8697,7 @@
         <v>41.1</v>
       </c>
       <c r="S11" t="n">
-        <v>88.7</v>
+        <v>93.2</v>
       </c>
       <c r="T11" t="n">
         <v>50</v>
@@ -8799,39 +8707,35 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr"/>
       <c r="AC11" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -9027,7 +8931,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -9046,7 +8950,7 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>34</v>
+        <v>33.5</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -9060,7 +8964,7 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P12" t="n">
@@ -9073,7 +8977,7 @@
         <v>41.1</v>
       </c>
       <c r="S12" t="n">
-        <v>90.40000000000001</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T12" t="n">
         <v>80</v>
@@ -9083,39 +8987,35 @@
       </c>
       <c r="V12" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr"/>
       <c r="AC12" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -9281,24 +9181,24 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>666152</t>
+          <t>676356</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>David Hamilton</t>
+          <t>Jonny DeLuca</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
           <t>MIL</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>TB</t>
-        </is>
-      </c>
       <c r="F13" t="inlineStr">
         <is>
           <t>2026-10-24T00:00:00Z</t>
@@ -9311,17 +9211,17 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Nick Martinez</t>
+          <t>Jacob Misiorowski</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>607259</t>
+          <t>694819</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -9330,7 +9230,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>32.7</v>
+        <v>32.8</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -9344,54 +9244,58 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Platoon Edge</t>
+          <t>Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P13" t="n">
-        <v>11.1</v>
+        <v>10.6</v>
       </c>
       <c r="Q13" t="n">
-        <v>34.3</v>
+        <v>18.6</v>
       </c>
       <c r="R13" t="n">
         <v>41.1</v>
       </c>
       <c r="S13" t="n">
-        <v>44.8</v>
+        <v>76.2</v>
       </c>
       <c r="T13" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U13" t="n">
-        <v>23.7</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="V13" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W13" t="inlineStr"/>
-      <c r="X13" t="inlineStr"/>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="Y13" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>not found on RotoWire</t>
-        </is>
-      </c>
+      <c r="AB13" t="inlineStr"/>
       <c r="AC13" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -9411,27 +9315,27 @@
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/18, 0 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.9% barrel, 22.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 4.9% barrel, 12.2 HR allowed</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
@@ -9441,97 +9345,97 @@
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>4.18</t>
+          <t>3.21</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>27.87</t>
+          <t>30.68</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>86.74</t>
+          <t>85.74</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>96.8019</t>
+          <t>97.7063</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>0.3169</t>
+          <t>0.3262</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
         <is>
-          <t>0.0967</t>
+          <t>0.0879</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>0.2712</t>
+          <t>0.2628</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
         <is>
-          <t>69.66</t>
+          <t>72.75</t>
         </is>
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>6.59</t>
+          <t>28.03</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>35.88</t>
+          <t>45.6</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>24.48</t>
+          <t>22.55</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>4.6</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>0.1042</t>
+          <t>0.151</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>6.86</t>
+          <t>4.89</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>33.38</t>
+          <t>34.56</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>87.39</t>
+          <t>87.74</t>
         </is>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
-          <t>0.4114</t>
+          <t>0.2817</t>
         </is>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
-          <t>0.1502</t>
+          <t>0.0996</t>
         </is>
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>28.96</t>
+          <t>25.57</t>
         </is>
       </c>
       <c r="BG13" t="inlineStr">
@@ -9557,12 +9461,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>806198</t>
+          <t>666152</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Cooper Pratt</t>
+          <t>David Hamilton</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -9587,7 +9491,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -9606,7 +9510,7 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>32.6</v>
+        <v>32.7</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -9620,11 +9524,11 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>No major boost</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P14" t="n">
-        <v>10.5</v>
+        <v>11.1</v>
       </c>
       <c r="Q14" t="n">
         <v>34.3</v>
@@ -9633,13 +9537,13 @@
         <v>41.1</v>
       </c>
       <c r="S14" t="n">
-        <v>64.3</v>
+        <v>44.8</v>
       </c>
       <c r="T14" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U14" t="n">
-        <v>24.9</v>
+        <v>23.7</v>
       </c>
       <c r="V14" t="inlineStr">
         <is>
@@ -9648,37 +9552,33 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X14" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Y14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB14" t="inlineStr"/>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD14" t="inlineStr"/>
@@ -9695,12 +9595,12 @@
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
@@ -9710,12 +9610,12 @@
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/21, 0 HR</t>
+          <t>Last 7 games: 5/18, 0 HR</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 6.9% barrel, 22.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.9% barrel, 22.0 HR allowed</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
@@ -9725,67 +9625,67 @@
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>3.2</t>
+          <t>4.18</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>27.4</t>
+          <t>27.87</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>86.74</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>96.5693</t>
+          <t>96.8019</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>0.362</t>
+          <t>0.3169</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
         <is>
-          <t>0.096</t>
+          <t>0.0967</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>0.315</t>
+          <t>0.2712</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
         <is>
-          <t>69.9</t>
+          <t>69.66</t>
         </is>
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>8.6</t>
+          <t>6.59</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>33.2</t>
+          <t>35.88</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>21.1</t>
+          <t>24.48</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>4.6</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>0.087</t>
+          <t>0.1042</t>
         </is>
       </c>
       <c r="BA14" t="inlineStr">
@@ -9841,12 +9741,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>686217</t>
+          <t>806198</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Sal Frelick</t>
+          <t>Cooper Pratt</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -9871,7 +9771,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -9890,7 +9790,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>31.6</v>
+        <v>32.6</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -9904,11 +9804,11 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Platoon Edge</t>
+          <t>No major boost</t>
         </is>
       </c>
       <c r="P15" t="n">
-        <v>5.4</v>
+        <v>10.5</v>
       </c>
       <c r="Q15" t="n">
         <v>34.3</v>
@@ -9917,44 +9817,48 @@
         <v>41.1</v>
       </c>
       <c r="S15" t="n">
-        <v>52.4</v>
+        <v>64.3</v>
       </c>
       <c r="T15" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U15" t="n">
-        <v>17.3</v>
+        <v>24.9</v>
       </c>
       <c r="V15" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W15" t="inlineStr"/>
-      <c r="X15" t="inlineStr"/>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="Y15" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>not found on RotoWire</t>
-        </is>
-      </c>
+      <c r="AB15" t="inlineStr"/>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AD15" t="inlineStr"/>
@@ -9971,12 +9875,12 @@
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
@@ -9986,12 +9890,12 @@
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/17, 0 HR</t>
+          <t>Last 7 games: 6/21, 0 HR</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.9% barrel, 22.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 6.9% barrel, 22.0 HR allowed</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
@@ -10001,67 +9905,67 @@
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>2.54</t>
+          <t>3.2</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>26.98</t>
+          <t>27.4</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>85.64</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>96.2217</t>
+          <t>96.5693</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>0.3285</t>
+          <t>0.362</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
         <is>
-          <t>0.0826</t>
+          <t>0.096</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>0.2864</t>
+          <t>0.315</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
         <is>
-          <t>68.24</t>
+          <t>69.9</t>
         </is>
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>3.76</t>
+          <t>8.6</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>39.46</t>
+          <t>33.2</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>20.9</t>
+          <t>21.1</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>6.4</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>0.0974</t>
+          <t>0.087</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
@@ -10117,12 +10021,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>680700</t>
+          <t>802415</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Richie Palacios</t>
+          <t>Chandler Simpson</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -10147,7 +10051,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -10166,7 +10070,7 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>30.6</v>
+        <v>32.2</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -10180,11 +10084,11 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P16" t="n">
-        <v>15.4</v>
+        <v>0.2</v>
       </c>
       <c r="Q16" t="n">
         <v>18.6</v>
@@ -10193,49 +10097,45 @@
         <v>41.1</v>
       </c>
       <c r="S16" t="n">
-        <v>47.9</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T16" t="n">
         <v>80</v>
       </c>
       <c r="U16" t="n">
-        <v>19.5</v>
+        <v>15.3</v>
       </c>
       <c r="V16" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X16" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Y16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr"/>
       <c r="AC16" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -10255,12 +10155,12 @@
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
@@ -10270,7 +10170,7 @@
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/20, 0 HR</t>
+          <t>Last 7 games: 6/27, 0 HR</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
@@ -10285,67 +10185,67 @@
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>4.57</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>33.39</t>
+          <t>14.71</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>87.31</t>
+          <t>83.88</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>97.1084</t>
+          <t>92.929</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>0.3655</t>
+          <t>0.3087</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
         <is>
-          <t>0.1018</t>
+          <t>0.0382</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>0.3213</t>
+          <t>0.2732</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
         <is>
-          <t>68.91</t>
+          <t>64.8</t>
         </is>
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>3.94</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>37.09</t>
+          <t>28.27</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>20.98</t>
+          <t>12.51</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>7.3</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>0.133</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
@@ -10401,24 +10301,24 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>676356</t>
+          <t>686217</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Jonny DeLuca</t>
+          <t>Sal Frelick</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
+          <t>MIL</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
           <t>TB</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>MIL</t>
-        </is>
-      </c>
       <c r="F17" t="inlineStr">
         <is>
           <t>2026-10-24T00:00:00Z</t>
@@ -10431,17 +10331,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Jacob Misiorowski</t>
+          <t>Nick Martinez</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>694819</t>
+          <t>607259</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -10450,7 +10350,7 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>30.5</v>
+        <v>31.6</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -10464,62 +10364,58 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Projected Lineup, Hot Hitter/Streak</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P17" t="n">
-        <v>10.6</v>
+        <v>5.4</v>
       </c>
       <c r="Q17" t="n">
-        <v>18.6</v>
+        <v>34.3</v>
       </c>
       <c r="R17" t="n">
         <v>41.1</v>
       </c>
       <c r="S17" t="n">
-        <v>59.8</v>
+        <v>52.4</v>
       </c>
       <c r="T17" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U17" t="n">
-        <v>70.59999999999999</v>
+        <v>17.3</v>
       </c>
       <c r="V17" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X17" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Y17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr"/>
       <c r="AC17" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -10539,27 +10435,27 @@
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>17</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 4/17, 0 HR</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 4.9% barrel, 12.2 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.9% barrel, 22.0 HR allowed</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
@@ -10569,97 +10465,97 @@
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>3.21</t>
+          <t>2.54</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>30.68</t>
+          <t>26.98</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>85.74</t>
+          <t>85.64</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>97.7063</t>
+          <t>96.2217</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>0.3262</t>
+          <t>0.3285</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
         <is>
-          <t>0.0879</t>
+          <t>0.0826</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>0.2628</t>
+          <t>0.2864</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
         <is>
-          <t>72.75</t>
+          <t>68.24</t>
         </is>
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>28.03</t>
+          <t>3.76</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>45.6</t>
+          <t>39.46</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>22.55</t>
+          <t>20.9</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>6.4</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>0.151</t>
+          <t>0.0974</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>4.89</t>
+          <t>6.86</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>34.56</t>
+          <t>33.38</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>87.74</t>
+          <t>87.39</t>
         </is>
       </c>
       <c r="BD17" t="inlineStr">
         <is>
-          <t>0.2817</t>
+          <t>0.4114</t>
         </is>
       </c>
       <c r="BE17" t="inlineStr">
         <is>
-          <t>0.0996</t>
+          <t>0.1502</t>
         </is>
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>25.57</t>
+          <t>28.96</t>
         </is>
       </c>
       <c r="BG17" t="inlineStr">
@@ -10685,12 +10581,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>802415</t>
+          <t>670764</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Chandler Simpson</t>
+          <t>Taylor Walls</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -10715,7 +10611,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -10734,7 +10630,7 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>30.1</v>
+        <v>26.5</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -10748,62 +10644,58 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P18" t="n">
-        <v>0.2</v>
+        <v>5.6</v>
       </c>
       <c r="Q18" t="n">
-        <v>18.6</v>
+        <v>17.3</v>
       </c>
       <c r="R18" t="n">
         <v>41.1</v>
       </c>
       <c r="S18" t="n">
-        <v>81.90000000000001</v>
+        <v>44.8</v>
       </c>
       <c r="T18" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="U18" t="n">
-        <v>15.3</v>
+        <v>27</v>
       </c>
       <c r="V18" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X18" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr"/>
       <c r="AC18" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -10828,7 +10720,7 @@
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
@@ -10838,12 +10730,12 @@
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/27, 0 HR</t>
+          <t>Last 7 games: 6/20, 0 HR</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 4.9% barrel, 12.2 HR allowed</t>
+          <t>switch hitter; pitcher baseline 4.9% barrel, 12.2 HR allowed</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
@@ -10853,67 +10745,67 @@
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>14.71</t>
+          <t>23.25</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>83.88</t>
+          <t>86.02</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>92.929</t>
+          <t>95.5424</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>0.3087</t>
+          <t>0.2754</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
         <is>
-          <t>0.0382</t>
+          <t>0.0794</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>0.2732</t>
+          <t>0.254</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
         <is>
-          <t>64.8</t>
+          <t>68.28</t>
         </is>
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>1.92</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>28.27</t>
+          <t>38.82</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>12.51</t>
+          <t>28.77</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.6</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.0829</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
@@ -10969,12 +10861,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>670764</t>
+          <t>810938</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Taylor Walls</t>
+          <t>Ben Williamson</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -10999,7 +10891,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -11018,7 +10910,7 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>25.9</v>
+        <v>26.3</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -11032,62 +10924,58 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>No major boost</t>
         </is>
       </c>
       <c r="P19" t="n">
-        <v>5.6</v>
+        <v>11.6</v>
       </c>
       <c r="Q19" t="n">
-        <v>17.3</v>
+        <v>18.6</v>
       </c>
       <c r="R19" t="n">
         <v>41.1</v>
       </c>
       <c r="S19" t="n">
-        <v>40.2</v>
+        <v>52.4</v>
       </c>
       <c r="T19" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="U19" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="V19" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X19" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="Y19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr"/>
       <c r="AC19" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -11107,12 +10995,12 @@
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
@@ -11122,12 +11010,12 @@
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/20, 0 HR</t>
+          <t>Last 7 games: 2/19, 0 HR</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 4.9% barrel, 12.2 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 4.9% barrel, 12.2 HR allowed</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
@@ -11137,67 +11025,67 @@
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>2.32</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>23.25</t>
+          <t>35.39</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>86.02</t>
+          <t>87.6</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>95.5424</t>
+          <t>98.4446</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>0.2754</t>
+          <t>0.3241</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
         <is>
-          <t>0.0794</t>
+          <t>0.0789</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>0.254</t>
+          <t>0.2809</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
         <is>
-          <t>68.28</t>
+          <t>69.49</t>
         </is>
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>1.92</t>
+          <t>10.53</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>38.82</t>
+          <t>27.55</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>28.77</t>
+          <t>14.95</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>2.6</t>
+          <t>2.4</t>
         </is>
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>0.0829</t>
+          <t>0.0731</t>
         </is>
       </c>
       <c r="BA19" t="inlineStr">

--- a/outputs/daily/hr_rankings_2026-10-23.xlsx
+++ b/outputs/daily/hr_rankings_2026-10-23.xlsx
@@ -784,7 +784,7 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>56.1</v>
+        <v>55.9</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -808,7 +808,7 @@
         <v>34.3</v>
       </c>
       <c r="R2" t="n">
-        <v>41.1</v>
+        <v>40.1</v>
       </c>
       <c r="S2" t="n">
         <v>100</v>
@@ -994,7 +994,7 @@
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>L To R</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
@@ -1064,7 +1064,7 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>51.6</v>
+        <v>51.5</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -1088,7 +1088,7 @@
         <v>34.3</v>
       </c>
       <c r="R3" t="n">
-        <v>41.1</v>
+        <v>40.1</v>
       </c>
       <c r="S3" t="n">
         <v>93.2</v>
@@ -1274,7 +1274,7 @@
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>L To R</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
@@ -1344,7 +1344,7 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>50.8</v>
+        <v>50.6</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -1368,7 +1368,7 @@
         <v>18.6</v>
       </c>
       <c r="R4" t="n">
-        <v>41.1</v>
+        <v>40.1</v>
       </c>
       <c r="S4" t="n">
         <v>94.90000000000001</v>
@@ -1554,7 +1554,7 @@
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>L To R</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
@@ -1624,7 +1624,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>49.4</v>
+        <v>49.2</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -1648,7 +1648,7 @@
         <v>18.6</v>
       </c>
       <c r="R5" t="n">
-        <v>41.1</v>
+        <v>40.1</v>
       </c>
       <c r="S5" t="n">
         <v>100</v>
@@ -1834,7 +1834,7 @@
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>L To R</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
@@ -1904,7 +1904,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>49</v>
+        <v>48.9</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -1928,7 +1928,7 @@
         <v>34.3</v>
       </c>
       <c r="R6" t="n">
-        <v>41.1</v>
+        <v>40.1</v>
       </c>
       <c r="S6" t="n">
         <v>96.59999999999999</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>L To R</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
@@ -2184,7 +2184,7 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>49</v>
+        <v>48.9</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -2208,7 +2208,7 @@
         <v>34.3</v>
       </c>
       <c r="R7" t="n">
-        <v>41.1</v>
+        <v>40.1</v>
       </c>
       <c r="S7" t="n">
         <v>86.40000000000001</v>
@@ -2394,7 +2394,7 @@
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>L To R</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
@@ -2464,7 +2464,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>48.5</v>
+        <v>48.3</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -2488,7 +2488,7 @@
         <v>34.3</v>
       </c>
       <c r="R8" t="n">
-        <v>41.1</v>
+        <v>40.1</v>
       </c>
       <c r="S8" t="n">
         <v>76.2</v>
@@ -2674,7 +2674,7 @@
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>L To R</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
@@ -2744,7 +2744,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>47.1</v>
+        <v>47</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -2768,7 +2768,7 @@
         <v>34.3</v>
       </c>
       <c r="R9" t="n">
-        <v>41.1</v>
+        <v>40.1</v>
       </c>
       <c r="S9" t="n">
         <v>94.90000000000001</v>
@@ -2954,7 +2954,7 @@
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>L To R</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
@@ -3024,7 +3024,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>44</v>
+        <v>43.8</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -3048,7 +3048,7 @@
         <v>18.6</v>
       </c>
       <c r="R10" t="n">
-        <v>41.1</v>
+        <v>40.1</v>
       </c>
       <c r="S10" t="n">
         <v>64.3</v>
@@ -3234,7 +3234,7 @@
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>L To R</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
@@ -3304,7 +3304,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>42.7</v>
+        <v>42.6</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -3328,7 +3328,7 @@
         <v>18.6</v>
       </c>
       <c r="R11" t="n">
-        <v>41.1</v>
+        <v>40.1</v>
       </c>
       <c r="S11" t="n">
         <v>93.2</v>
@@ -3514,7 +3514,7 @@
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>L To R</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
@@ -3584,7 +3584,7 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>33.5</v>
+        <v>33.3</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -3608,7 +3608,7 @@
         <v>18.6</v>
       </c>
       <c r="R12" t="n">
-        <v>41.1</v>
+        <v>40.1</v>
       </c>
       <c r="S12" t="n">
         <v>86.40000000000001</v>
@@ -3794,7 +3794,7 @@
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>L To R</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
@@ -3864,7 +3864,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>32.8</v>
+        <v>32.7</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -3888,7 +3888,7 @@
         <v>18.6</v>
       </c>
       <c r="R13" t="n">
-        <v>41.1</v>
+        <v>40.1</v>
       </c>
       <c r="S13" t="n">
         <v>76.2</v>
@@ -4074,7 +4074,7 @@
       </c>
       <c r="BG13" t="inlineStr">
         <is>
-          <t>L To R</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BH13" t="inlineStr">
@@ -4144,7 +4144,7 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>32.7</v>
+        <v>32.6</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -4168,7 +4168,7 @@
         <v>34.3</v>
       </c>
       <c r="R14" t="n">
-        <v>41.1</v>
+        <v>40.1</v>
       </c>
       <c r="S14" t="n">
         <v>44.8</v>
@@ -4354,7 +4354,7 @@
       </c>
       <c r="BG14" t="inlineStr">
         <is>
-          <t>L To R</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BH14" t="inlineStr">
@@ -4424,7 +4424,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>32.6</v>
+        <v>32.5</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -4448,7 +4448,7 @@
         <v>34.3</v>
       </c>
       <c r="R15" t="n">
-        <v>41.1</v>
+        <v>40.1</v>
       </c>
       <c r="S15" t="n">
         <v>64.3</v>
@@ -4634,7 +4634,7 @@
       </c>
       <c r="BG15" t="inlineStr">
         <is>
-          <t>L To R</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BH15" t="inlineStr">
@@ -4704,7 +4704,7 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>32.2</v>
+        <v>32.1</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -4728,7 +4728,7 @@
         <v>18.6</v>
       </c>
       <c r="R16" t="n">
-        <v>41.1</v>
+        <v>40.1</v>
       </c>
       <c r="S16" t="n">
         <v>96.59999999999999</v>
@@ -4914,7 +4914,7 @@
       </c>
       <c r="BG16" t="inlineStr">
         <is>
-          <t>L To R</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BH16" t="inlineStr">
@@ -4984,7 +4984,7 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>31.6</v>
+        <v>31.4</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -5008,7 +5008,7 @@
         <v>34.3</v>
       </c>
       <c r="R17" t="n">
-        <v>41.1</v>
+        <v>40.1</v>
       </c>
       <c r="S17" t="n">
         <v>52.4</v>
@@ -5194,7 +5194,7 @@
       </c>
       <c r="BG17" t="inlineStr">
         <is>
-          <t>L To R</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BH17" t="inlineStr">
@@ -5264,7 +5264,7 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>26.5</v>
+        <v>26.4</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -5288,7 +5288,7 @@
         <v>17.3</v>
       </c>
       <c r="R18" t="n">
-        <v>41.1</v>
+        <v>40.1</v>
       </c>
       <c r="S18" t="n">
         <v>44.8</v>
@@ -5474,7 +5474,7 @@
       </c>
       <c r="BG18" t="inlineStr">
         <is>
-          <t>L To R</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BH18" t="inlineStr">
@@ -5544,7 +5544,7 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>26.3</v>
+        <v>26.2</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -5568,7 +5568,7 @@
         <v>18.6</v>
       </c>
       <c r="R19" t="n">
-        <v>41.1</v>
+        <v>40.1</v>
       </c>
       <c r="S19" t="n">
         <v>52.4</v>
@@ -5754,7 +5754,7 @@
       </c>
       <c r="BG19" t="inlineStr">
         <is>
-          <t>L To R</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BH19" t="inlineStr">
@@ -6150,7 +6150,7 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>56.1</v>
+        <v>55.9</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -6174,7 +6174,7 @@
         <v>34.3</v>
       </c>
       <c r="R2" t="n">
-        <v>41.1</v>
+        <v>40.1</v>
       </c>
       <c r="S2" t="n">
         <v>100</v>
@@ -6360,7 +6360,7 @@
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>L To R</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
@@ -6430,7 +6430,7 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>51.6</v>
+        <v>51.5</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -6454,7 +6454,7 @@
         <v>34.3</v>
       </c>
       <c r="R3" t="n">
-        <v>41.1</v>
+        <v>40.1</v>
       </c>
       <c r="S3" t="n">
         <v>93.2</v>
@@ -6640,7 +6640,7 @@
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>L To R</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
@@ -6710,7 +6710,7 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>50.8</v>
+        <v>50.6</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -6734,7 +6734,7 @@
         <v>18.6</v>
       </c>
       <c r="R4" t="n">
-        <v>41.1</v>
+        <v>40.1</v>
       </c>
       <c r="S4" t="n">
         <v>94.90000000000001</v>
@@ -6920,7 +6920,7 @@
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>L To R</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
@@ -6990,7 +6990,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>49.4</v>
+        <v>49.2</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -7014,7 +7014,7 @@
         <v>18.6</v>
       </c>
       <c r="R5" t="n">
-        <v>41.1</v>
+        <v>40.1</v>
       </c>
       <c r="S5" t="n">
         <v>100</v>
@@ -7200,7 +7200,7 @@
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>L To R</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
@@ -7270,7 +7270,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>49</v>
+        <v>48.9</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -7294,7 +7294,7 @@
         <v>34.3</v>
       </c>
       <c r="R6" t="n">
-        <v>41.1</v>
+        <v>40.1</v>
       </c>
       <c r="S6" t="n">
         <v>96.59999999999999</v>
@@ -7480,7 +7480,7 @@
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>L To R</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
@@ -7550,7 +7550,7 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>49</v>
+        <v>48.9</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -7574,7 +7574,7 @@
         <v>34.3</v>
       </c>
       <c r="R7" t="n">
-        <v>41.1</v>
+        <v>40.1</v>
       </c>
       <c r="S7" t="n">
         <v>86.40000000000001</v>
@@ -7760,7 +7760,7 @@
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>L To R</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
@@ -7830,7 +7830,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>48.5</v>
+        <v>48.3</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -7854,7 +7854,7 @@
         <v>34.3</v>
       </c>
       <c r="R8" t="n">
-        <v>41.1</v>
+        <v>40.1</v>
       </c>
       <c r="S8" t="n">
         <v>76.2</v>
@@ -8040,7 +8040,7 @@
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>L To R</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
@@ -8110,7 +8110,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>47.1</v>
+        <v>47</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -8134,7 +8134,7 @@
         <v>34.3</v>
       </c>
       <c r="R9" t="n">
-        <v>41.1</v>
+        <v>40.1</v>
       </c>
       <c r="S9" t="n">
         <v>94.90000000000001</v>
@@ -8320,7 +8320,7 @@
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>L To R</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
@@ -8390,7 +8390,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>44</v>
+        <v>43.8</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -8414,7 +8414,7 @@
         <v>18.6</v>
       </c>
       <c r="R10" t="n">
-        <v>41.1</v>
+        <v>40.1</v>
       </c>
       <c r="S10" t="n">
         <v>64.3</v>
@@ -8600,7 +8600,7 @@
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>L To R</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
@@ -8670,7 +8670,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>42.7</v>
+        <v>42.6</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -8694,7 +8694,7 @@
         <v>18.6</v>
       </c>
       <c r="R11" t="n">
-        <v>41.1</v>
+        <v>40.1</v>
       </c>
       <c r="S11" t="n">
         <v>93.2</v>
@@ -8880,7 +8880,7 @@
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>L To R</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
@@ -8950,7 +8950,7 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>33.5</v>
+        <v>33.3</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -8974,7 +8974,7 @@
         <v>18.6</v>
       </c>
       <c r="R12" t="n">
-        <v>41.1</v>
+        <v>40.1</v>
       </c>
       <c r="S12" t="n">
         <v>86.40000000000001</v>
@@ -9160,7 +9160,7 @@
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>L To R</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
@@ -9230,7 +9230,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>32.8</v>
+        <v>32.7</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -9254,7 +9254,7 @@
         <v>18.6</v>
       </c>
       <c r="R13" t="n">
-        <v>41.1</v>
+        <v>40.1</v>
       </c>
       <c r="S13" t="n">
         <v>76.2</v>
@@ -9440,7 +9440,7 @@
       </c>
       <c r="BG13" t="inlineStr">
         <is>
-          <t>L To R</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BH13" t="inlineStr">
@@ -9510,7 +9510,7 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>32.7</v>
+        <v>32.6</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -9534,7 +9534,7 @@
         <v>34.3</v>
       </c>
       <c r="R14" t="n">
-        <v>41.1</v>
+        <v>40.1</v>
       </c>
       <c r="S14" t="n">
         <v>44.8</v>
@@ -9720,7 +9720,7 @@
       </c>
       <c r="BG14" t="inlineStr">
         <is>
-          <t>L To R</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BH14" t="inlineStr">
@@ -9790,7 +9790,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>32.6</v>
+        <v>32.5</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -9814,7 +9814,7 @@
         <v>34.3</v>
       </c>
       <c r="R15" t="n">
-        <v>41.1</v>
+        <v>40.1</v>
       </c>
       <c r="S15" t="n">
         <v>64.3</v>
@@ -10000,7 +10000,7 @@
       </c>
       <c r="BG15" t="inlineStr">
         <is>
-          <t>L To R</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BH15" t="inlineStr">
@@ -10070,7 +10070,7 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>32.2</v>
+        <v>32.1</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -10094,7 +10094,7 @@
         <v>18.6</v>
       </c>
       <c r="R16" t="n">
-        <v>41.1</v>
+        <v>40.1</v>
       </c>
       <c r="S16" t="n">
         <v>96.59999999999999</v>
@@ -10280,7 +10280,7 @@
       </c>
       <c r="BG16" t="inlineStr">
         <is>
-          <t>L To R</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BH16" t="inlineStr">
@@ -10350,7 +10350,7 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>31.6</v>
+        <v>31.4</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -10374,7 +10374,7 @@
         <v>34.3</v>
       </c>
       <c r="R17" t="n">
-        <v>41.1</v>
+        <v>40.1</v>
       </c>
       <c r="S17" t="n">
         <v>52.4</v>
@@ -10560,7 +10560,7 @@
       </c>
       <c r="BG17" t="inlineStr">
         <is>
-          <t>L To R</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BH17" t="inlineStr">
@@ -10630,7 +10630,7 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>26.5</v>
+        <v>26.4</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -10654,7 +10654,7 @@
         <v>17.3</v>
       </c>
       <c r="R18" t="n">
-        <v>41.1</v>
+        <v>40.1</v>
       </c>
       <c r="S18" t="n">
         <v>44.8</v>
@@ -10840,7 +10840,7 @@
       </c>
       <c r="BG18" t="inlineStr">
         <is>
-          <t>L To R</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BH18" t="inlineStr">
@@ -10910,7 +10910,7 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>26.3</v>
+        <v>26.2</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -10934,7 +10934,7 @@
         <v>18.6</v>
       </c>
       <c r="R19" t="n">
-        <v>41.1</v>
+        <v>40.1</v>
       </c>
       <c r="S19" t="n">
         <v>52.4</v>
@@ -11120,7 +11120,7 @@
       </c>
       <c r="BG19" t="inlineStr">
         <is>
-          <t>L To R</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BH19" t="inlineStr">
